--- a/2026/BRIN 3219/ENERO/BRIN3219-EXPENSAS-Enero.xlsx
+++ b/2026/BRIN 3219/ENERO/BRIN3219-EXPENSAS-Enero.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\BRIN 3219\ENERO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{874F0399-111D-428A-8BCB-23189DE2EE83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD4EF1DD-9F3B-4AF9-B13E-039D83E3B30B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="27" r:id="rId1"/>
@@ -18,8 +18,8 @@
     <sheet name="EXTRAORDINARIAS" sheetId="28" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">Planilla!$A$1:$N$33</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$H$104</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">Planilla!$A$1:$O$32</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$H$96</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="160">
   <si>
     <t>U.F.</t>
   </si>
@@ -249,9 +249,6 @@
     <t>Ingreso por expensas alquiler Piso 6 UF 24</t>
   </si>
   <si>
-    <t>Ingreso por alquiler Piso 6 UF 24</t>
-  </si>
-  <si>
     <t xml:space="preserve">TOTAL </t>
   </si>
   <si>
@@ -373,9 +370,6 @@
   </si>
   <si>
     <t>Paula</t>
-  </si>
-  <si>
-    <t>y expensas</t>
   </si>
   <si>
     <t>MP 1148</t>
@@ -432,9 +426,6 @@
     <t>Eliseo</t>
   </si>
   <si>
-    <t>Ingreso por pago de Expensas - MARZO</t>
-  </si>
-  <si>
     <t>HORAS EXTRAS FUMIGACION</t>
   </si>
   <si>
@@ -483,12 +474,6 @@
     <t xml:space="preserve">Ascensor </t>
   </si>
   <si>
-    <t>La UF 1.7 tiene a favor este dinero para cubrir sus extraordinarias -  aquí llevaremos la cuenta de como se va descontando el mismo</t>
-  </si>
-  <si>
-    <t>Ingreso 14/11</t>
-  </si>
-  <si>
     <t>Reemplazo Sra. Monica</t>
   </si>
   <si>
@@ -501,27 +486,9 @@
     <t>Ordinarios:</t>
   </si>
   <si>
-    <t>Extraordinarias nov</t>
-  </si>
-  <si>
     <t>Le queda a favor esto actualmente</t>
   </si>
   <si>
-    <t>SAC</t>
-  </si>
-  <si>
-    <t>Martin - Camaras arreglo</t>
-  </si>
-  <si>
-    <t>Nico Plagas</t>
-  </si>
-  <si>
-    <t>Citta Cerrajeria - Ajuste de manijon exterior y colocacon de pomo fijo de bronce pulido</t>
-  </si>
-  <si>
-    <t>Julio Doartero - Colocacion de rejilla</t>
-  </si>
-  <si>
     <t>INGRESO</t>
   </si>
   <si>
@@ -537,13 +504,25 @@
     <t>Egresos por gastos mes - ENERO</t>
   </si>
   <si>
-    <t>Julio Doartero - Emergencia</t>
-  </si>
-  <si>
-    <t>Lema ascensores - Pago parcial arreglo guiadores Resta abonar $1.481.119,5</t>
-  </si>
-  <si>
-    <t>lema</t>
+    <t>Destapacion AySa</t>
+  </si>
+  <si>
+    <t>Julio Doartero - Cambio de canilla robada</t>
+  </si>
+  <si>
+    <t>Lema - Quedaba pendiente de abonar $1.481.119,50 - Se abona $1.310.527,79 : Resta abonar $170.591,71</t>
+  </si>
+  <si>
+    <t>Nico Plagas - Desratizacion</t>
+  </si>
+  <si>
+    <t>Ingreso por alquiler Piso 6 UF 24 y Expensas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ingreso por pago de Expensas </t>
+  </si>
+  <si>
+    <t>Extraordinarias</t>
   </si>
 </sst>
 </file>
@@ -1352,7 +1331,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="239">
+  <cellXfs count="243">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
@@ -1558,9 +1537,6 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="18" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="21" fillId="2" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="16" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1652,6 +1628,90 @@
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="44" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="164" fontId="30" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="22" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1667,18 +1727,6 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="22" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="22" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1697,9 +1745,6 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1709,75 +1754,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="1" fontId="23" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1802,8 +1778,21 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="30" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="18" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="18" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="2" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="2" fillId="8" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hipervínculo" xfId="2" builtinId="8"/>
@@ -2250,7 +2239,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:K109"/>
+  <dimension ref="A1:K101"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="28.6640625" customWidth="1"/>
@@ -2275,23 +2264,23 @@
     </row>
     <row r="2" spans="1:9" ht="48" customHeight="1">
       <c r="A2" s="10"/>
-      <c r="D2" s="189"/>
-      <c r="E2" s="190"/>
-      <c r="F2" s="190"/>
-      <c r="G2" s="190"/>
-      <c r="H2" s="191"/>
+      <c r="D2" s="216"/>
+      <c r="E2" s="217"/>
+      <c r="F2" s="217"/>
+      <c r="G2" s="217"/>
+      <c r="H2" s="218"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="10"/>
       <c r="D3" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="204">
+      <c r="E3" s="226">
         <v>1153202676</v>
       </c>
-      <c r="F3" s="204"/>
-      <c r="G3" s="204"/>
-      <c r="H3" s="205"/>
+      <c r="F3" s="226"/>
+      <c r="G3" s="226"/>
+      <c r="H3" s="227"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="10"/>
@@ -2319,7 +2308,7 @@
         <v>9</v>
       </c>
       <c r="G6" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="H6" s="11"/>
     </row>
@@ -2338,10 +2327,10 @@
         <v>66</v>
       </c>
       <c r="F8" s="89" t="s">
-        <v>161</v>
+        <v>150</v>
       </c>
       <c r="G8" s="19" t="s">
-        <v>160</v>
+        <v>149</v>
       </c>
       <c r="H8" s="20"/>
     </row>
@@ -2370,14 +2359,14 @@
       <c r="H11" s="11"/>
     </row>
     <row r="12" spans="1:9" ht="67.5" hidden="1" customHeight="1">
-      <c r="A12" s="201"/>
-      <c r="B12" s="202"/>
-      <c r="C12" s="202"/>
-      <c r="D12" s="202"/>
-      <c r="E12" s="202"/>
-      <c r="F12" s="202"/>
-      <c r="G12" s="202"/>
-      <c r="H12" s="203"/>
+      <c r="A12" s="224"/>
+      <c r="B12" s="187"/>
+      <c r="C12" s="187"/>
+      <c r="D12" s="187"/>
+      <c r="E12" s="187"/>
+      <c r="F12" s="187"/>
+      <c r="G12" s="187"/>
+      <c r="H12" s="225"/>
     </row>
     <row r="13" spans="1:9" ht="13.5" customHeight="1">
       <c r="A13" s="12"/>
@@ -2390,1268 +2379,1158 @@
       <c r="H13" s="13"/>
     </row>
     <row r="14" spans="1:9" ht="15.6">
-      <c r="A14" s="210" t="s">
-        <v>124</v>
-      </c>
-      <c r="B14" s="210"/>
-      <c r="C14" s="210"/>
-      <c r="D14" s="210"/>
-      <c r="E14" s="210"/>
-      <c r="F14" s="210"/>
-      <c r="G14" s="210"/>
-      <c r="H14" s="210"/>
+      <c r="A14" s="198" t="s">
+        <v>122</v>
+      </c>
+      <c r="B14" s="198"/>
+      <c r="C14" s="198"/>
+      <c r="D14" s="198"/>
+      <c r="E14" s="198"/>
+      <c r="F14" s="198"/>
+      <c r="G14" s="198"/>
+      <c r="H14" s="198"/>
     </row>
     <row r="15" spans="1:9">
-      <c r="A15" s="176" t="s">
+      <c r="A15" s="175" t="s">
+        <v>137</v>
+      </c>
+      <c r="B15" s="138"/>
+      <c r="C15" s="138"/>
+      <c r="D15" s="138"/>
+      <c r="E15" s="138"/>
+      <c r="F15" s="138"/>
+      <c r="G15" s="138"/>
+      <c r="H15" s="73">
+        <v>326678.40000000002</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="A16" s="175" t="s">
+        <v>85</v>
+      </c>
+      <c r="B16" s="138"/>
+      <c r="C16" s="138"/>
+      <c r="D16" s="138"/>
+      <c r="E16" s="138"/>
+      <c r="F16" s="138"/>
+      <c r="G16" s="138"/>
+      <c r="H16" s="73">
+        <v>-51451.839999999997</v>
+      </c>
+      <c r="I16" s="7"/>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17" s="175" t="s">
+        <v>116</v>
+      </c>
+      <c r="B17" s="138"/>
+      <c r="C17" s="138"/>
+      <c r="D17" s="138"/>
+      <c r="E17" s="138"/>
+      <c r="F17" s="138"/>
+      <c r="G17" s="138"/>
+      <c r="H17" s="73">
+        <v>0.44</v>
+      </c>
+      <c r="I17" s="7"/>
+    </row>
+    <row r="18" spans="1:9">
+      <c r="A18" s="175" t="s">
+        <v>73</v>
+      </c>
+      <c r="B18" s="138"/>
+      <c r="C18" s="138"/>
+      <c r="D18" s="138"/>
+      <c r="E18" s="138"/>
+      <c r="F18" s="138"/>
+      <c r="G18" s="138"/>
+      <c r="H18" s="69">
+        <f>SUM(H15:H17)</f>
+        <v>275227.00000000006</v>
+      </c>
+      <c r="I18" s="7"/>
+    </row>
+    <row r="19" spans="1:9" ht="0.75" customHeight="1">
+      <c r="A19" s="220" t="s">
         <v>140</v>
       </c>
-      <c r="B15" s="139"/>
-      <c r="C15" s="139"/>
-      <c r="D15" s="139"/>
-      <c r="E15" s="139"/>
-      <c r="F15" s="139"/>
-      <c r="G15" s="139"/>
-      <c r="H15" s="73">
-        <v>302625.5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9">
-      <c r="A16" s="176" t="s">
+      <c r="B19" s="220"/>
+      <c r="C19" s="220"/>
+      <c r="D19" s="220"/>
+      <c r="E19" s="220"/>
+      <c r="F19" s="220"/>
+      <c r="G19" s="220"/>
+      <c r="H19" s="220"/>
+    </row>
+    <row r="20" spans="1:9" hidden="1">
+      <c r="A20" s="175" t="s">
+        <v>143</v>
+      </c>
+      <c r="B20" s="138"/>
+      <c r="C20" s="138"/>
+      <c r="D20" s="138"/>
+      <c r="E20" s="138"/>
+      <c r="F20" s="138"/>
+      <c r="G20" s="138"/>
+      <c r="H20" s="73"/>
+    </row>
+    <row r="21" spans="1:9" hidden="1">
+      <c r="A21" s="175" t="s">
+        <v>144</v>
+      </c>
+      <c r="B21" s="138"/>
+      <c r="C21" s="138"/>
+      <c r="D21" s="138"/>
+      <c r="E21" s="138"/>
+      <c r="F21" s="138"/>
+      <c r="G21" s="138"/>
+      <c r="H21" s="73"/>
+    </row>
+    <row r="22" spans="1:9" hidden="1">
+      <c r="A22" s="175" t="s">
+        <v>73</v>
+      </c>
+      <c r="B22" s="138"/>
+      <c r="C22" s="138"/>
+      <c r="D22" s="138"/>
+      <c r="E22" s="138"/>
+      <c r="F22" s="138"/>
+      <c r="G22" s="138"/>
+      <c r="H22" s="69">
+        <f>SUM(H20:H21)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
+      <c r="A23" s="219" t="s">
+        <v>127</v>
+      </c>
+      <c r="B23" s="219"/>
+      <c r="C23" s="219"/>
+      <c r="D23" s="219"/>
+      <c r="E23" s="219"/>
+      <c r="F23" s="219"/>
+      <c r="G23" s="219"/>
+      <c r="H23" s="219"/>
+    </row>
+    <row r="24" spans="1:9">
+      <c r="A24" s="138" t="s">
+        <v>135</v>
+      </c>
+      <c r="B24" s="138"/>
+      <c r="C24" s="138"/>
+      <c r="D24" s="138"/>
+      <c r="E24" s="138"/>
+      <c r="F24" s="138"/>
+      <c r="G24" s="138"/>
+      <c r="H24" s="73">
+        <v>32000</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
+      <c r="A25" s="138"/>
+      <c r="B25" s="138"/>
+      <c r="C25" s="138"/>
+      <c r="D25" s="138"/>
+      <c r="E25" s="138"/>
+      <c r="F25" s="138"/>
+      <c r="G25" s="138"/>
+      <c r="H25" s="73"/>
+    </row>
+    <row r="26" spans="1:9">
+      <c r="A26" s="138" t="s">
+        <v>73</v>
+      </c>
+      <c r="B26" s="138"/>
+      <c r="C26" s="138"/>
+      <c r="D26" s="138"/>
+      <c r="E26" s="138"/>
+      <c r="F26" s="138"/>
+      <c r="G26" s="138"/>
+      <c r="H26" s="69">
+        <f>SUM(H24:H25)</f>
+        <v>32000</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" ht="14.25" customHeight="1">
+      <c r="A27" s="199" t="s">
         <v>86</v>
       </c>
-      <c r="B16" s="139"/>
-      <c r="C16" s="139"/>
-      <c r="D16" s="139"/>
-      <c r="E16" s="139"/>
-      <c r="F16" s="139"/>
-      <c r="G16" s="139"/>
-      <c r="H16" s="73">
-        <v>-47663.53</v>
-      </c>
-      <c r="I16" s="7"/>
-    </row>
-    <row r="17" spans="1:9">
-      <c r="A17" s="176" t="s">
-        <v>118</v>
-      </c>
-      <c r="B17" s="139"/>
-      <c r="C17" s="139"/>
-      <c r="D17" s="139"/>
-      <c r="E17" s="139"/>
-      <c r="F17" s="139"/>
-      <c r="G17" s="139"/>
-      <c r="H17" s="73">
-        <v>0.5</v>
-      </c>
-      <c r="I17" s="7"/>
-    </row>
-    <row r="18" spans="1:9">
-      <c r="A18" s="176" t="s">
-        <v>154</v>
-      </c>
-      <c r="B18" s="139"/>
-      <c r="C18" s="139"/>
-      <c r="D18" s="139"/>
-      <c r="E18" s="139"/>
-      <c r="F18" s="139"/>
-      <c r="G18" s="139"/>
-      <c r="H18" s="73">
-        <v>283132.11</v>
-      </c>
-      <c r="I18" s="7"/>
-    </row>
-    <row r="19" spans="1:9">
-      <c r="A19" s="176" t="s">
-        <v>86</v>
-      </c>
-      <c r="B19" s="139"/>
-      <c r="C19" s="139"/>
-      <c r="D19" s="139"/>
-      <c r="E19" s="139"/>
-      <c r="F19" s="139"/>
-      <c r="G19" s="139"/>
-      <c r="H19" s="73">
-        <v>-44593.3</v>
-      </c>
-      <c r="I19" s="7"/>
-    </row>
-    <row r="20" spans="1:9">
-      <c r="A20" s="176" t="s">
-        <v>118</v>
-      </c>
-      <c r="B20" s="139"/>
-      <c r="C20" s="139"/>
-      <c r="D20" s="139"/>
-      <c r="E20" s="139"/>
-      <c r="F20" s="139"/>
-      <c r="G20" s="139"/>
-      <c r="H20" s="73">
-        <v>0.19</v>
-      </c>
-      <c r="I20" s="7"/>
-    </row>
-    <row r="21" spans="1:9">
-      <c r="A21" s="176" t="s">
-        <v>74</v>
-      </c>
-      <c r="B21" s="139"/>
-      <c r="C21" s="139"/>
-      <c r="D21" s="139"/>
-      <c r="E21" s="139"/>
-      <c r="F21" s="139"/>
-      <c r="G21" s="139"/>
-      <c r="H21" s="69">
-        <f>SUM(H15:H20)</f>
-        <v>493501.47</v>
-      </c>
-      <c r="I21" s="7"/>
-    </row>
-    <row r="22" spans="1:9" ht="0.75" customHeight="1">
-      <c r="A22" s="197" t="s">
-        <v>143</v>
-      </c>
-      <c r="B22" s="197"/>
-      <c r="C22" s="197"/>
-      <c r="D22" s="197"/>
-      <c r="E22" s="197"/>
-      <c r="F22" s="197"/>
-      <c r="G22" s="197"/>
-      <c r="H22" s="197"/>
-    </row>
-    <row r="23" spans="1:9" hidden="1">
-      <c r="A23" s="176" t="s">
-        <v>148</v>
-      </c>
-      <c r="B23" s="139"/>
-      <c r="C23" s="139"/>
-      <c r="D23" s="139"/>
-      <c r="E23" s="139"/>
-      <c r="F23" s="139"/>
-      <c r="G23" s="139"/>
-      <c r="H23" s="73"/>
-    </row>
-    <row r="24" spans="1:9" hidden="1">
-      <c r="A24" s="176" t="s">
-        <v>149</v>
-      </c>
-      <c r="B24" s="139"/>
-      <c r="C24" s="139"/>
-      <c r="D24" s="139"/>
-      <c r="E24" s="139"/>
-      <c r="F24" s="139"/>
-      <c r="G24" s="139"/>
-      <c r="H24" s="73"/>
-    </row>
-    <row r="25" spans="1:9" hidden="1">
-      <c r="A25" s="176" t="s">
-        <v>74</v>
-      </c>
-      <c r="B25" s="139"/>
-      <c r="C25" s="139"/>
-      <c r="D25" s="139"/>
-      <c r="E25" s="139"/>
-      <c r="F25" s="139"/>
-      <c r="G25" s="139"/>
-      <c r="H25" s="69">
-        <f>SUM(H23:H24)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9">
-      <c r="A26" s="196" t="s">
-        <v>130</v>
-      </c>
-      <c r="B26" s="196"/>
-      <c r="C26" s="196"/>
-      <c r="D26" s="196"/>
-      <c r="E26" s="196"/>
-      <c r="F26" s="196"/>
-      <c r="G26" s="196"/>
-      <c r="H26" s="196"/>
-    </row>
-    <row r="27" spans="1:9">
-      <c r="A27" s="139" t="s">
-        <v>138</v>
-      </c>
-      <c r="B27" s="139"/>
-      <c r="C27" s="139"/>
-      <c r="D27" s="139"/>
-      <c r="E27" s="139"/>
-      <c r="F27" s="139"/>
-      <c r="G27" s="139"/>
-      <c r="H27" s="73">
-        <v>32000</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9">
-      <c r="A28" s="139"/>
-      <c r="B28" s="139"/>
-      <c r="C28" s="139"/>
-      <c r="D28" s="139"/>
-      <c r="E28" s="139"/>
-      <c r="F28" s="139"/>
-      <c r="G28" s="139"/>
+      <c r="B27" s="199"/>
+      <c r="C27" s="199"/>
+      <c r="D27" s="199"/>
+      <c r="E27" s="199"/>
+      <c r="F27" s="199"/>
+      <c r="G27" s="199"/>
+      <c r="H27" s="199"/>
+    </row>
+    <row r="28" spans="1:9" hidden="1">
+      <c r="A28" s="175"/>
+      <c r="B28" s="138"/>
+      <c r="C28" s="138"/>
+      <c r="D28" s="138"/>
+      <c r="E28" s="138"/>
+      <c r="F28" s="138"/>
+      <c r="G28" s="138"/>
       <c r="H28" s="73"/>
     </row>
     <row r="29" spans="1:9">
-      <c r="A29" s="139" t="s">
-        <v>74</v>
-      </c>
-      <c r="B29" s="139"/>
-      <c r="C29" s="139"/>
-      <c r="D29" s="139"/>
-      <c r="E29" s="139"/>
-      <c r="F29" s="139"/>
-      <c r="G29" s="139"/>
-      <c r="H29" s="69">
-        <f>SUM(H27:H28)</f>
-        <v>32000</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A30" s="192" t="s">
-        <v>87</v>
-      </c>
-      <c r="B30" s="192"/>
-      <c r="C30" s="192"/>
-      <c r="D30" s="192"/>
-      <c r="E30" s="192"/>
-      <c r="F30" s="192"/>
-      <c r="G30" s="192"/>
-      <c r="H30" s="192"/>
-    </row>
-    <row r="31" spans="1:9" hidden="1">
-      <c r="A31" s="176"/>
-      <c r="B31" s="139"/>
-      <c r="C31" s="139"/>
-      <c r="D31" s="139"/>
-      <c r="E31" s="139"/>
-      <c r="F31" s="139"/>
-      <c r="G31" s="139"/>
-      <c r="H31" s="73"/>
-    </row>
-    <row r="32" spans="1:9">
-      <c r="A32" s="176" t="s">
-        <v>79</v>
-      </c>
-      <c r="B32" s="177"/>
-      <c r="C32" s="139"/>
-      <c r="D32" s="139"/>
-      <c r="E32" s="139"/>
-      <c r="F32" s="139"/>
-      <c r="G32" s="139"/>
-      <c r="H32" s="237">
+      <c r="A29" s="175" t="s">
+        <v>78</v>
+      </c>
+      <c r="B29" s="176"/>
+      <c r="C29" s="138"/>
+      <c r="D29" s="138"/>
+      <c r="E29" s="138"/>
+      <c r="F29" s="138"/>
+      <c r="G29" s="138"/>
+      <c r="H29" s="73">
         <f>59104.24+2928.79+26359.09</f>
         <v>88392.12</v>
       </c>
     </row>
-    <row r="33" spans="1:8">
-      <c r="A33" s="139" t="s">
-        <v>139</v>
-      </c>
-      <c r="B33" s="139"/>
-      <c r="C33" s="139"/>
-      <c r="D33" s="139"/>
-      <c r="E33" s="139"/>
-      <c r="F33" s="139"/>
-      <c r="G33" s="139"/>
+    <row r="30" spans="1:9">
+      <c r="A30" s="138" t="s">
+        <v>136</v>
+      </c>
+      <c r="B30" s="138"/>
+      <c r="C30" s="138"/>
+      <c r="D30" s="138"/>
+      <c r="E30" s="138"/>
+      <c r="F30" s="138"/>
+      <c r="G30" s="138"/>
+      <c r="H30" s="73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9">
+      <c r="A31" s="138" t="s">
+        <v>72</v>
+      </c>
+      <c r="B31" s="138"/>
+      <c r="C31" s="138"/>
+      <c r="D31" s="138"/>
+      <c r="E31" s="138"/>
+      <c r="F31" s="138"/>
+      <c r="G31" s="138"/>
+      <c r="H31" s="69">
+        <f>SUM(H28:H30)</f>
+        <v>88392.12</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9">
+      <c r="A32" s="199" t="s">
+        <v>128</v>
+      </c>
+      <c r="B32" s="199"/>
+      <c r="C32" s="199"/>
+      <c r="D32" s="199"/>
+      <c r="E32" s="199"/>
+      <c r="F32" s="199"/>
+      <c r="G32" s="199"/>
+      <c r="H32" s="199"/>
+    </row>
+    <row r="33" spans="1:11" ht="14.25" customHeight="1">
+      <c r="A33" s="138" t="s">
+        <v>138</v>
+      </c>
+      <c r="B33" s="138"/>
+      <c r="C33" s="138"/>
+      <c r="D33" s="138"/>
+      <c r="E33" s="138"/>
+      <c r="F33" s="138"/>
+      <c r="G33" s="138"/>
       <c r="H33" s="73">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8">
-      <c r="A34" s="139" t="s">
+        <v>1531896.82</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11">
+      <c r="A34" s="177" t="s">
+        <v>98</v>
+      </c>
+      <c r="B34" s="138"/>
+      <c r="C34" s="138"/>
+      <c r="D34" s="138"/>
+      <c r="E34" s="138"/>
+      <c r="F34" s="138"/>
+      <c r="G34" s="138"/>
+      <c r="H34" s="73">
+        <v>96402.21</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11">
+      <c r="A35" s="138" t="s">
         <v>73</v>
       </c>
-      <c r="B34" s="139"/>
-      <c r="C34" s="139"/>
-      <c r="D34" s="139"/>
-      <c r="E34" s="139"/>
-      <c r="F34" s="139"/>
-      <c r="G34" s="139"/>
-      <c r="H34" s="69">
-        <f>SUM(H31:H33)</f>
-        <v>88392.12</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8">
-      <c r="A35" s="192" t="s">
+      <c r="B35" s="138"/>
+      <c r="C35" s="138"/>
+      <c r="D35" s="138"/>
+      <c r="E35" s="138"/>
+      <c r="F35" s="138"/>
+      <c r="G35" s="138"/>
+      <c r="H35" s="178">
+        <f>SUM(H33:H34)</f>
+        <v>1628299.03</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11">
+      <c r="A36" s="198" t="s">
+        <v>129</v>
+      </c>
+      <c r="B36" s="198"/>
+      <c r="C36" s="198"/>
+      <c r="D36" s="198"/>
+      <c r="E36" s="198"/>
+      <c r="F36" s="198"/>
+      <c r="G36" s="198"/>
+      <c r="H36" s="198"/>
+    </row>
+    <row r="37" spans="1:11">
+      <c r="A37" s="80" t="s">
+        <v>68</v>
+      </c>
+      <c r="B37" s="138"/>
+      <c r="C37" s="138"/>
+      <c r="D37" s="138"/>
+      <c r="E37" s="138"/>
+      <c r="F37" s="138"/>
+      <c r="G37" s="138"/>
+      <c r="H37" s="73">
+        <v>85000</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11">
+      <c r="A38" s="80" t="s">
+        <v>155</v>
+      </c>
+      <c r="B38" s="138"/>
+      <c r="C38" s="138"/>
+      <c r="D38" s="138"/>
+      <c r="E38" s="138"/>
+      <c r="F38" s="138"/>
+      <c r="G38" s="138"/>
+      <c r="H38" s="73">
+        <f>385625+924902.79</f>
+        <v>1310527.79</v>
+      </c>
+      <c r="I38" s="236"/>
+    </row>
+    <row r="39" spans="1:11">
+      <c r="A39" s="80" t="s">
+        <v>156</v>
+      </c>
+      <c r="B39" s="138"/>
+      <c r="C39" s="138"/>
+      <c r="D39" s="138"/>
+      <c r="E39" s="138"/>
+      <c r="F39" s="138"/>
+      <c r="G39" s="138"/>
+      <c r="H39" s="73">
+        <v>200000</v>
+      </c>
+      <c r="I39" s="7"/>
+    </row>
+    <row r="40" spans="1:11">
+      <c r="A40" s="138" t="s">
+        <v>69</v>
+      </c>
+      <c r="B40" s="138"/>
+      <c r="C40" s="138"/>
+      <c r="D40" s="138"/>
+      <c r="E40" s="138"/>
+      <c r="F40" s="138"/>
+      <c r="G40" s="138"/>
+      <c r="H40" s="73">
+        <v>22411.599999999999</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11">
+      <c r="A41" s="138" t="s">
+        <v>151</v>
+      </c>
+      <c r="B41" s="138"/>
+      <c r="C41" s="138"/>
+      <c r="D41" s="138"/>
+      <c r="E41" s="138"/>
+      <c r="F41" s="138"/>
+      <c r="G41" s="138"/>
+      <c r="H41" s="73">
+        <v>65000</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11">
+      <c r="A42" s="138" t="s">
+        <v>153</v>
+      </c>
+      <c r="B42" s="138"/>
+      <c r="C42" s="138"/>
+      <c r="D42" s="138"/>
+      <c r="E42" s="138"/>
+      <c r="F42" s="138"/>
+      <c r="G42" s="138"/>
+      <c r="H42" s="73">
+        <v>60000</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11">
+      <c r="A43" s="80" t="s">
+        <v>154</v>
+      </c>
+      <c r="B43" s="138"/>
+      <c r="C43" s="138"/>
+      <c r="D43" s="138"/>
+      <c r="E43" s="138"/>
+      <c r="F43" s="138"/>
+      <c r="G43" s="138"/>
+      <c r="H43" s="73">
+        <v>85000</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11">
+      <c r="A44" s="138" t="s">
+        <v>73</v>
+      </c>
+      <c r="B44" s="138"/>
+      <c r="C44" s="138"/>
+      <c r="D44" s="138"/>
+      <c r="E44" s="138"/>
+      <c r="F44" s="138"/>
+      <c r="G44" s="138"/>
+      <c r="H44" s="69">
+        <f>SUM(H37:H43)</f>
+        <v>1827939.3900000001</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11">
+      <c r="A45" s="198" t="s">
+        <v>130</v>
+      </c>
+      <c r="B45" s="198"/>
+      <c r="C45" s="198"/>
+      <c r="D45" s="198"/>
+      <c r="E45" s="198"/>
+      <c r="F45" s="198"/>
+      <c r="G45" s="198"/>
+      <c r="H45" s="198"/>
+    </row>
+    <row r="46" spans="1:11">
+      <c r="A46" s="138" t="s">
+        <v>70</v>
+      </c>
+      <c r="B46" s="138"/>
+      <c r="C46" s="138"/>
+      <c r="D46" s="138"/>
+      <c r="E46" s="138"/>
+      <c r="F46" s="138"/>
+      <c r="G46" s="138"/>
+      <c r="H46" s="73">
+        <v>170100</v>
+      </c>
+      <c r="J46" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11">
+      <c r="A47" s="138" t="s">
+        <v>115</v>
+      </c>
+      <c r="B47" s="138"/>
+      <c r="C47" s="138"/>
+      <c r="D47" s="138"/>
+      <c r="E47" s="138"/>
+      <c r="F47" s="138"/>
+      <c r="G47" s="138"/>
+      <c r="H47" s="73">
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11">
+      <c r="A48" s="138" t="s">
+        <v>72</v>
+      </c>
+      <c r="B48" s="138"/>
+      <c r="C48" s="138"/>
+      <c r="D48" s="138"/>
+      <c r="E48" s="138"/>
+      <c r="F48" s="138"/>
+      <c r="G48" s="138"/>
+      <c r="H48" s="178">
+        <f>SUM(H46:H47)</f>
+        <v>205100</v>
+      </c>
+      <c r="K48" s="7"/>
+    </row>
+    <row r="49" spans="1:9" s="6" customFormat="1">
+      <c r="A49" s="200" t="s">
         <v>131</v>
       </c>
-      <c r="B35" s="192"/>
-      <c r="C35" s="192"/>
-      <c r="D35" s="192"/>
-      <c r="E35" s="192"/>
-      <c r="F35" s="192"/>
-      <c r="G35" s="192"/>
-      <c r="H35" s="192"/>
-    </row>
-    <row r="36" spans="1:8" ht="14.25" customHeight="1">
-      <c r="A36" s="139" t="s">
-        <v>141</v>
-      </c>
-      <c r="B36" s="139"/>
-      <c r="C36" s="139"/>
-      <c r="D36" s="139"/>
-      <c r="E36" s="139"/>
-      <c r="F36" s="139"/>
-      <c r="G36" s="139"/>
-      <c r="H36" s="73">
-        <v>759994.39</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8">
-      <c r="A37" s="178" t="s">
-        <v>99</v>
-      </c>
-      <c r="B37" s="139"/>
-      <c r="C37" s="139"/>
-      <c r="D37" s="139"/>
-      <c r="E37" s="139"/>
-      <c r="F37" s="139"/>
-      <c r="G37" s="139"/>
-      <c r="H37" s="73">
-        <v>83788.34</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8">
-      <c r="A38" s="139" t="s">
+      <c r="B49" s="201"/>
+      <c r="C49" s="201"/>
+      <c r="D49" s="201"/>
+      <c r="E49" s="201"/>
+      <c r="F49" s="201"/>
+      <c r="G49" s="201"/>
+      <c r="H49" s="202"/>
+    </row>
+    <row r="50" spans="1:9" s="6" customFormat="1">
+      <c r="A50" s="80" t="s">
+        <v>117</v>
+      </c>
+      <c r="B50" s="80"/>
+      <c r="C50" s="80"/>
+      <c r="D50" s="80"/>
+      <c r="E50" s="80"/>
+      <c r="F50" s="80"/>
+      <c r="G50" s="80"/>
+      <c r="H50" s="73">
+        <v>24990</v>
+      </c>
+      <c r="I50" s="60"/>
+    </row>
+    <row r="51" spans="1:9" s="6" customFormat="1">
+      <c r="A51" s="80" t="s">
+        <v>73</v>
+      </c>
+      <c r="B51" s="80"/>
+      <c r="C51" s="80"/>
+      <c r="D51" s="80"/>
+      <c r="E51" s="80"/>
+      <c r="F51" s="80"/>
+      <c r="G51" s="80"/>
+      <c r="H51" s="69">
+        <f>SUM(H50)</f>
+        <v>24990</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" s="6" customFormat="1">
+      <c r="A52" s="198" t="s">
+        <v>132</v>
+      </c>
+      <c r="B52" s="198"/>
+      <c r="C52" s="198"/>
+      <c r="D52" s="198"/>
+      <c r="E52" s="198"/>
+      <c r="F52" s="198"/>
+      <c r="G52" s="198"/>
+      <c r="H52" s="198"/>
+    </row>
+    <row r="53" spans="1:9" s="6" customFormat="1">
+      <c r="A53" s="80"/>
+      <c r="B53" s="80"/>
+      <c r="C53" s="80"/>
+      <c r="D53" s="80"/>
+      <c r="E53" s="80"/>
+      <c r="F53" s="80"/>
+      <c r="G53" s="80"/>
+      <c r="H53" s="73"/>
+    </row>
+    <row r="54" spans="1:9" s="6" customFormat="1">
+      <c r="A54" s="80"/>
+      <c r="B54" s="80"/>
+      <c r="C54" s="80"/>
+      <c r="D54" s="80"/>
+      <c r="E54" s="80"/>
+      <c r="F54" s="80"/>
+      <c r="G54" s="80"/>
+      <c r="H54" s="73"/>
+    </row>
+    <row r="55" spans="1:9" s="6" customFormat="1">
+      <c r="A55" s="174"/>
+      <c r="B55" s="174"/>
+      <c r="C55" s="174"/>
+      <c r="D55" s="174"/>
+      <c r="E55" s="174"/>
+      <c r="F55" s="174"/>
+      <c r="G55" s="174"/>
+      <c r="H55" s="173">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" s="6" customFormat="1" ht="21" customHeight="1">
+      <c r="A56" s="80" t="s">
         <v>74</v>
       </c>
-      <c r="B38" s="139"/>
-      <c r="C38" s="139"/>
-      <c r="D38" s="139"/>
-      <c r="E38" s="139"/>
-      <c r="F38" s="139"/>
-      <c r="G38" s="139"/>
-      <c r="H38" s="179">
-        <f>SUM(H36:H37)</f>
-        <v>843782.73</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8">
-      <c r="A39" s="210" t="s">
-        <v>132</v>
-      </c>
-      <c r="B39" s="210"/>
-      <c r="C39" s="210"/>
-      <c r="D39" s="210"/>
-      <c r="E39" s="210"/>
-      <c r="F39" s="210"/>
-      <c r="G39" s="210"/>
-      <c r="H39" s="210"/>
-    </row>
-    <row r="40" spans="1:8">
-      <c r="A40" s="80" t="s">
-        <v>68</v>
-      </c>
-      <c r="B40" s="139"/>
-      <c r="C40" s="139"/>
-      <c r="D40" s="139"/>
-      <c r="E40" s="139"/>
-      <c r="F40" s="139"/>
-      <c r="G40" s="139"/>
-      <c r="H40" s="73">
-        <v>85000</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8">
-      <c r="A41" s="238" t="s">
-        <v>166</v>
-      </c>
-      <c r="B41" s="139"/>
-      <c r="C41" s="139"/>
-      <c r="D41" s="139"/>
-      <c r="E41" s="139"/>
-      <c r="F41" s="139"/>
-      <c r="G41" s="139"/>
-      <c r="H41" s="237">
-        <v>385625</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8">
-      <c r="A42" s="238" t="s">
-        <v>166</v>
-      </c>
-      <c r="B42" s="139"/>
-      <c r="C42" s="139"/>
-      <c r="D42" s="139"/>
-      <c r="E42" s="139"/>
-      <c r="F42" s="139"/>
-      <c r="G42" s="139"/>
-      <c r="H42" s="237">
-        <v>85000</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8">
-      <c r="A43" s="80" t="s">
-        <v>165</v>
-      </c>
-      <c r="B43" s="139"/>
-      <c r="C43" s="139"/>
-      <c r="D43" s="139"/>
-      <c r="E43" s="139"/>
-      <c r="F43" s="139"/>
-      <c r="G43" s="139"/>
-      <c r="H43" s="73">
-        <f>1000000+712434.25</f>
-        <v>1712434.25</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8">
-      <c r="A44" s="139" t="s">
-        <v>69</v>
-      </c>
-      <c r="B44" s="139"/>
-      <c r="C44" s="139"/>
-      <c r="D44" s="139"/>
-      <c r="E44" s="139"/>
-      <c r="F44" s="139"/>
-      <c r="G44" s="139"/>
-      <c r="H44" s="237">
-        <v>22411.599999999999</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8">
-      <c r="A45" s="139" t="s">
+      <c r="B56" s="80"/>
+      <c r="C56" s="80"/>
+      <c r="D56" s="80"/>
+      <c r="E56" s="80"/>
+      <c r="F56" s="80"/>
+      <c r="G56" s="80"/>
+      <c r="H56" s="69">
+        <f>SUM(H53:H55)</f>
+        <v>0</v>
+      </c>
+      <c r="I56" s="60"/>
+    </row>
+    <row r="57" spans="1:9" s="6" customFormat="1" ht="18" customHeight="1">
+      <c r="A57" s="200"/>
+      <c r="B57" s="201"/>
+      <c r="C57" s="201"/>
+      <c r="D57" s="201"/>
+      <c r="E57" s="201"/>
+      <c r="F57" s="201"/>
+      <c r="G57" s="201"/>
+      <c r="H57" s="202"/>
+    </row>
+    <row r="58" spans="1:9" s="6" customFormat="1" ht="23.25" hidden="1" customHeight="1">
+      <c r="A58" s="81"/>
+      <c r="B58" s="82"/>
+      <c r="C58" s="82"/>
+      <c r="D58" s="82"/>
+      <c r="E58" s="82"/>
+      <c r="F58" s="82"/>
+      <c r="G58" s="82"/>
+      <c r="H58" s="157">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" s="6" customFormat="1" ht="20.25" hidden="1" customHeight="1">
+      <c r="A59" s="158"/>
+      <c r="B59" s="159"/>
+      <c r="C59" s="159"/>
+      <c r="D59" s="159"/>
+      <c r="E59" s="159"/>
+      <c r="F59" s="159"/>
+      <c r="G59" s="159"/>
+      <c r="H59" s="160">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" s="6" customFormat="1" ht="18" hidden="1" customHeight="1">
+      <c r="A60" s="161"/>
+      <c r="B60" s="162"/>
+      <c r="C60" s="162"/>
+      <c r="D60" s="162"/>
+      <c r="E60" s="162"/>
+      <c r="F60" s="162"/>
+      <c r="G60" s="162"/>
+      <c r="H60" s="157">
+        <f>H58+H59</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" s="6" customFormat="1" ht="18" hidden="1" customHeight="1">
+      <c r="A61" s="211" t="s">
+        <v>80</v>
+      </c>
+      <c r="B61" s="212"/>
+      <c r="C61" s="212"/>
+      <c r="D61" s="212"/>
+      <c r="E61" s="212"/>
+      <c r="F61" s="212"/>
+      <c r="G61" s="212"/>
+      <c r="H61" s="163">
+        <f>H56</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" s="6" customFormat="1" ht="18" customHeight="1">
+      <c r="A62" s="214"/>
+      <c r="B62" s="214"/>
+      <c r="C62" s="214"/>
+      <c r="D62" s="214"/>
+      <c r="E62" s="214"/>
+      <c r="F62" s="214"/>
+      <c r="G62" s="214"/>
+      <c r="H62" s="214"/>
+    </row>
+    <row r="63" spans="1:9" s="6" customFormat="1" ht="86.25" hidden="1" customHeight="1">
+      <c r="A63" s="215"/>
+      <c r="B63" s="215"/>
+      <c r="C63" s="215"/>
+      <c r="D63" s="215"/>
+      <c r="E63" s="215"/>
+      <c r="F63" s="215"/>
+      <c r="G63" s="215"/>
+      <c r="H63" s="215"/>
+    </row>
+    <row r="64" spans="1:9" s="6" customFormat="1" ht="18" customHeight="1">
+      <c r="A64" s="213" t="s">
+        <v>82</v>
+      </c>
+      <c r="B64" s="213"/>
+      <c r="C64" s="213"/>
+      <c r="D64" s="213"/>
+      <c r="E64" s="213"/>
+      <c r="F64" s="213"/>
+      <c r="G64" s="213"/>
+      <c r="H64" s="164"/>
+    </row>
+    <row r="65" spans="1:11" s="6" customFormat="1" ht="26.25" customHeight="1">
+      <c r="A65" s="221"/>
+      <c r="B65" s="222"/>
+      <c r="C65" s="222"/>
+      <c r="D65" s="222"/>
+      <c r="E65" s="222"/>
+      <c r="F65" s="222"/>
+      <c r="G65" s="223"/>
+      <c r="H65" s="73"/>
+    </row>
+    <row r="66" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1">
+      <c r="A66" s="128" t="s">
+        <v>73</v>
+      </c>
+      <c r="B66" s="80"/>
+      <c r="C66" s="80"/>
+      <c r="D66" s="80"/>
+      <c r="E66" s="80"/>
+      <c r="F66" s="80"/>
+      <c r="G66" s="80"/>
+      <c r="H66" s="69">
+        <f>SUM(H65:H65)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1" thickBot="1">
+      <c r="A67" s="129"/>
+      <c r="B67" s="129"/>
+      <c r="C67" s="129"/>
+      <c r="D67" s="129"/>
+      <c r="E67" s="129"/>
+      <c r="F67" s="129"/>
+      <c r="G67" s="129"/>
+      <c r="H67" s="130"/>
+    </row>
+    <row r="68" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1" thickBot="1">
+      <c r="A68" s="194" t="s">
+        <v>81</v>
+      </c>
+      <c r="B68" s="195"/>
+      <c r="C68" s="195"/>
+      <c r="D68" s="195"/>
+      <c r="E68" s="195"/>
+      <c r="F68" s="195"/>
+      <c r="G68" s="195"/>
+      <c r="H68" s="131">
+        <f>H66</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1" thickBot="1">
+      <c r="A69" s="206" t="s">
+        <v>87</v>
+      </c>
+      <c r="B69" s="207"/>
+      <c r="C69" s="207"/>
+      <c r="D69" s="207"/>
+      <c r="E69" s="207"/>
+      <c r="F69" s="207"/>
+      <c r="G69" s="208"/>
+      <c r="H69" s="131"/>
+    </row>
+    <row r="70" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1" thickBot="1">
+      <c r="A70" s="206" t="s">
+        <v>92</v>
+      </c>
+      <c r="B70" s="207"/>
+      <c r="C70" s="207"/>
+      <c r="D70" s="207"/>
+      <c r="E70" s="207"/>
+      <c r="F70" s="207"/>
+      <c r="G70" s="208"/>
+      <c r="H70" s="131">
+        <v>1000000</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11" ht="18">
+      <c r="A71" s="194" t="s">
+        <v>88</v>
+      </c>
+      <c r="B71" s="195"/>
+      <c r="C71" s="195"/>
+      <c r="D71" s="195"/>
+      <c r="E71" s="195"/>
+      <c r="F71" s="195"/>
+      <c r="G71" s="195"/>
+      <c r="H71" s="131">
+        <f>H26+H35+H44+H48+H51+H31+H18+H22</f>
+        <v>4081947.54</v>
+      </c>
+      <c r="J71" s="172"/>
+      <c r="K71" s="143"/>
+    </row>
+    <row r="72" spans="1:11" ht="18">
+      <c r="A72" s="203" t="s">
+        <v>120</v>
+      </c>
+      <c r="B72" s="204"/>
+      <c r="C72" s="204"/>
+      <c r="D72" s="204"/>
+      <c r="E72" s="204"/>
+      <c r="F72" s="204"/>
+      <c r="G72" s="205"/>
+      <c r="H72" s="132">
+        <f>H69+H71</f>
+        <v>4081947.54</v>
+      </c>
+      <c r="I72" s="127"/>
+      <c r="J72" s="186"/>
+      <c r="K72" s="186"/>
+    </row>
+    <row r="73" spans="1:11" ht="18">
+      <c r="A73" s="203" t="s">
+        <v>93</v>
+      </c>
+      <c r="B73" s="204"/>
+      <c r="C73" s="204"/>
+      <c r="D73" s="204"/>
+      <c r="E73" s="204"/>
+      <c r="F73" s="204"/>
+      <c r="G73" s="205"/>
+      <c r="H73" s="133">
+        <f>H70+H68</f>
+        <v>1000000</v>
+      </c>
+      <c r="J73" s="143"/>
+    </row>
+    <row r="74" spans="1:11" ht="20.25" customHeight="1" thickBot="1">
+      <c r="A74" s="209" t="s">
+        <v>83</v>
+      </c>
+      <c r="B74" s="210"/>
+      <c r="C74" s="210"/>
+      <c r="D74" s="210"/>
+      <c r="E74" s="210"/>
+      <c r="F74" s="210"/>
+      <c r="G74" s="210"/>
+      <c r="H74" s="134">
+        <f>H71+H68</f>
+        <v>4081947.54</v>
+      </c>
+      <c r="J74" s="7"/>
+    </row>
+    <row r="75" spans="1:11" ht="18" hidden="1">
+      <c r="A75" s="196" t="s">
+        <v>17</v>
+      </c>
+      <c r="B75" s="197"/>
+      <c r="C75" s="197"/>
+      <c r="D75" s="197"/>
+      <c r="E75" s="197"/>
+      <c r="F75" s="197"/>
+      <c r="G75" s="197"/>
+      <c r="H75" s="135">
+        <f>H60</f>
+        <v>0</v>
+      </c>
+      <c r="J75" s="7"/>
+    </row>
+    <row r="76" spans="1:11" ht="18" hidden="1">
+      <c r="A76" s="136"/>
+      <c r="B76" s="136"/>
+      <c r="C76" s="136"/>
+      <c r="D76" s="136"/>
+      <c r="E76" s="136"/>
+      <c r="F76" s="136"/>
+      <c r="G76" s="136"/>
+      <c r="H76" s="137"/>
+      <c r="J76" s="7"/>
+    </row>
+    <row r="77" spans="1:11" ht="18" hidden="1">
+      <c r="A77" s="136"/>
+      <c r="B77" s="136"/>
+      <c r="C77" s="136"/>
+      <c r="D77" s="136"/>
+      <c r="E77" s="136"/>
+      <c r="F77" s="136"/>
+      <c r="G77" s="136"/>
+      <c r="H77" s="137"/>
+      <c r="J77" s="7"/>
+    </row>
+    <row r="78" spans="1:11" ht="18" hidden="1">
+      <c r="A78" s="136"/>
+      <c r="B78" s="136"/>
+      <c r="C78" s="136"/>
+      <c r="D78" s="136"/>
+      <c r="E78" s="136"/>
+      <c r="F78" s="136"/>
+      <c r="G78" s="136"/>
+      <c r="H78" s="137"/>
+      <c r="J78" s="7"/>
+    </row>
+    <row r="79" spans="1:11" ht="14.25" customHeight="1">
+      <c r="A79" s="138"/>
+      <c r="B79" s="138"/>
+      <c r="C79" s="138"/>
+      <c r="D79" s="138"/>
+      <c r="E79" s="138"/>
+      <c r="F79" s="138"/>
+      <c r="G79" s="138"/>
+      <c r="H79" s="138"/>
+    </row>
+    <row r="80" spans="1:11" ht="18">
+      <c r="A80" s="191" t="s">
+        <v>10</v>
+      </c>
+      <c r="B80" s="192"/>
+      <c r="C80" s="192"/>
+      <c r="D80" s="192"/>
+      <c r="E80" s="192"/>
+      <c r="F80" s="192"/>
+      <c r="G80" s="192"/>
+      <c r="H80" s="193"/>
+    </row>
+    <row r="81" spans="1:11" ht="18">
+      <c r="A81" s="139" t="s">
+        <v>12</v>
+      </c>
+      <c r="B81" s="140"/>
+      <c r="C81" s="140"/>
+      <c r="D81" s="140"/>
+      <c r="E81" s="140"/>
+      <c r="F81" s="140"/>
+      <c r="G81" s="140"/>
+      <c r="H81" s="141">
+        <v>3532612.5527224625</v>
+      </c>
+    </row>
+    <row r="82" spans="1:11">
+      <c r="A82" s="81" t="s">
+        <v>158</v>
+      </c>
+      <c r="B82" s="82"/>
+      <c r="C82" s="82"/>
+      <c r="D82" s="82"/>
+      <c r="E82" s="82"/>
+      <c r="F82" s="82"/>
+      <c r="G82" s="82"/>
+      <c r="H82" s="142">
+        <f>Planilla!G32</f>
+        <v>3926249.2638619998</v>
+      </c>
+    </row>
+    <row r="83" spans="1:11">
+      <c r="A83" s="78" t="s">
+        <v>152</v>
+      </c>
+      <c r="B83" s="79"/>
+      <c r="C83" s="79"/>
+      <c r="D83" s="79"/>
+      <c r="E83" s="79"/>
+      <c r="F83" s="79"/>
+      <c r="G83" s="79"/>
+      <c r="H83" s="182">
+        <f>-(H74)</f>
+        <v>-4081947.54</v>
+      </c>
+    </row>
+    <row r="84" spans="1:11">
+      <c r="A84" s="78" t="s">
+        <v>84</v>
+      </c>
+      <c r="B84" s="79"/>
+      <c r="C84" s="79"/>
+      <c r="D84" s="79"/>
+      <c r="E84" s="79"/>
+      <c r="F84" s="79"/>
+      <c r="G84" s="79"/>
+      <c r="H84" s="182">
+        <f>-H61</f>
+        <v>0</v>
+      </c>
+      <c r="K84" s="6"/>
+    </row>
+    <row r="85" spans="1:11">
+      <c r="A85" s="78" t="s">
         <v>157</v>
       </c>
-      <c r="B45" s="139"/>
-      <c r="C45" s="139"/>
-      <c r="D45" s="139"/>
-      <c r="E45" s="139"/>
-      <c r="F45" s="139"/>
-      <c r="G45" s="139"/>
-      <c r="H45" s="73">
-        <v>60000</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8">
-      <c r="A46" s="139" t="s">
-        <v>162</v>
-      </c>
-      <c r="B46" s="139"/>
-      <c r="C46" s="139"/>
-      <c r="D46" s="139"/>
-      <c r="E46" s="139"/>
-      <c r="F46" s="139"/>
-      <c r="G46" s="139"/>
-      <c r="H46" s="237">
-        <v>65000</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8">
-      <c r="A47" s="139" t="s">
-        <v>155</v>
-      </c>
-      <c r="B47" s="139"/>
-      <c r="C47" s="139"/>
-      <c r="D47" s="139"/>
-      <c r="E47" s="139"/>
-      <c r="F47" s="139"/>
-      <c r="G47" s="139"/>
-      <c r="H47" s="73">
-        <v>135000</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8">
-      <c r="A48" s="80" t="s">
-        <v>164</v>
-      </c>
-      <c r="B48" s="139"/>
-      <c r="C48" s="139"/>
-      <c r="D48" s="139"/>
-      <c r="E48" s="139"/>
-      <c r="F48" s="139"/>
-      <c r="G48" s="139"/>
-      <c r="H48" s="237">
-        <v>85000</v>
-      </c>
-    </row>
-    <row r="49" spans="1:11">
-      <c r="A49" s="80" t="s">
-        <v>158</v>
-      </c>
-      <c r="B49" s="139"/>
-      <c r="C49" s="139"/>
-      <c r="D49" s="139"/>
-      <c r="E49" s="139"/>
-      <c r="F49" s="139"/>
-      <c r="G49" s="139"/>
-      <c r="H49" s="73">
-        <v>35000</v>
-      </c>
-    </row>
-    <row r="50" spans="1:11" ht="14.25" customHeight="1">
-      <c r="A50" s="80" t="s">
-        <v>156</v>
-      </c>
-      <c r="B50" s="139"/>
-      <c r="C50" s="139"/>
-      <c r="D50" s="139"/>
-      <c r="E50" s="139"/>
-      <c r="F50" s="139"/>
-      <c r="G50" s="139"/>
-      <c r="H50" s="73">
-        <v>30000</v>
-      </c>
-    </row>
-    <row r="51" spans="1:11">
-      <c r="A51" s="139" t="s">
-        <v>74</v>
-      </c>
-      <c r="B51" s="139"/>
-      <c r="C51" s="139"/>
-      <c r="D51" s="139"/>
-      <c r="E51" s="139"/>
-      <c r="F51" s="139"/>
-      <c r="G51" s="139"/>
-      <c r="H51" s="69">
-        <f>SUM(H40:H50)</f>
-        <v>2700470.85</v>
-      </c>
-    </row>
-    <row r="52" spans="1:11">
-      <c r="A52" s="210" t="s">
-        <v>133</v>
-      </c>
-      <c r="B52" s="210"/>
-      <c r="C52" s="210"/>
-      <c r="D52" s="210"/>
-      <c r="E52" s="210"/>
-      <c r="F52" s="210"/>
-      <c r="G52" s="210"/>
-      <c r="H52" s="210"/>
-    </row>
-    <row r="53" spans="1:11">
-      <c r="A53" s="139" t="s">
-        <v>70</v>
-      </c>
-      <c r="B53" s="139"/>
-      <c r="C53" s="139"/>
-      <c r="D53" s="139"/>
-      <c r="E53" s="139"/>
-      <c r="F53" s="139"/>
-      <c r="G53" s="139"/>
-      <c r="H53" s="73">
-        <v>170100</v>
-      </c>
-      <c r="J53" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="54" spans="1:11">
-      <c r="A54" s="139" t="s">
-        <v>117</v>
-      </c>
-      <c r="B54" s="139"/>
-      <c r="C54" s="139"/>
-      <c r="D54" s="139"/>
-      <c r="E54" s="139"/>
-      <c r="F54" s="139"/>
-      <c r="G54" s="139"/>
-      <c r="H54" s="73">
-        <v>35000</v>
-      </c>
-    </row>
-    <row r="55" spans="1:11">
-      <c r="A55" s="139"/>
-      <c r="B55" s="139"/>
-      <c r="C55" s="139"/>
-      <c r="D55" s="139"/>
-      <c r="E55" s="139"/>
-      <c r="F55" s="139"/>
-      <c r="G55" s="139"/>
-      <c r="H55" s="73"/>
-    </row>
-    <row r="56" spans="1:11">
-      <c r="A56" s="139" t="s">
-        <v>73</v>
-      </c>
-      <c r="B56" s="139"/>
-      <c r="C56" s="139"/>
-      <c r="D56" s="139"/>
-      <c r="E56" s="139"/>
-      <c r="F56" s="139"/>
-      <c r="G56" s="139"/>
-      <c r="H56" s="179">
-        <f>SUM(H53:H55)</f>
-        <v>205100</v>
-      </c>
-      <c r="K56" s="7"/>
-    </row>
-    <row r="57" spans="1:11" s="6" customFormat="1">
-      <c r="A57" s="211" t="s">
-        <v>134</v>
-      </c>
-      <c r="B57" s="212"/>
-      <c r="C57" s="212"/>
-      <c r="D57" s="212"/>
-      <c r="E57" s="212"/>
-      <c r="F57" s="212"/>
-      <c r="G57" s="212"/>
-      <c r="H57" s="213"/>
-    </row>
-    <row r="58" spans="1:11" s="6" customFormat="1">
-      <c r="A58" s="80" t="s">
+      <c r="B85" s="79"/>
+      <c r="C85" s="79"/>
+      <c r="D85" s="79"/>
+      <c r="E85" s="79"/>
+      <c r="F85" s="79"/>
+      <c r="G85" s="79"/>
+      <c r="H85" s="122">
+        <v>133680</v>
+      </c>
+    </row>
+    <row r="86" spans="1:11">
+      <c r="A86" s="78" t="s">
+        <v>71</v>
+      </c>
+      <c r="B86" s="79"/>
+      <c r="C86" s="79"/>
+      <c r="D86" s="79"/>
+      <c r="E86" s="79"/>
+      <c r="F86" s="79"/>
+      <c r="G86" s="79"/>
+      <c r="H86" s="122">
+        <v>53562.275882499991</v>
+      </c>
+      <c r="I86" s="143"/>
+    </row>
+    <row r="87" spans="1:11">
+      <c r="A87" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="B87" s="83"/>
+      <c r="C87" s="4"/>
+      <c r="D87" s="4"/>
+      <c r="E87" s="4"/>
+      <c r="F87" s="4"/>
+      <c r="G87" s="4"/>
+      <c r="H87" s="98"/>
+    </row>
+    <row r="88" spans="1:11" ht="18">
+      <c r="A88" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="B88" s="23"/>
+      <c r="C88" s="23"/>
+      <c r="D88" s="23"/>
+      <c r="E88" s="23"/>
+      <c r="F88" s="23"/>
+      <c r="G88" s="23"/>
+      <c r="H88" s="84">
+        <f>SUM(H81:H87)</f>
+        <v>3564156.5524669625</v>
+      </c>
+    </row>
+    <row r="89" spans="1:11" ht="15" thickBot="1"/>
+    <row r="90" spans="1:11" ht="16.2" thickBot="1">
+      <c r="A90" s="188" t="s">
+        <v>97</v>
+      </c>
+      <c r="B90" s="189"/>
+      <c r="C90" s="189"/>
+      <c r="D90" s="189"/>
+      <c r="E90" s="189"/>
+      <c r="F90" s="189"/>
+      <c r="G90" s="189"/>
+      <c r="H90" s="190"/>
+    </row>
+    <row r="91" spans="1:11" ht="15.6">
+      <c r="A91" s="87" t="s">
+        <v>12</v>
+      </c>
+      <c r="B91" s="87"/>
+      <c r="C91" s="87"/>
+      <c r="D91" s="87"/>
+      <c r="E91" s="87"/>
+      <c r="F91" s="87"/>
+      <c r="G91" s="87"/>
+      <c r="H91" s="88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:11">
+      <c r="A92" s="61" t="s">
         <v>119</v>
       </c>
-      <c r="B58" s="80"/>
-      <c r="C58" s="80"/>
-      <c r="D58" s="80"/>
-      <c r="E58" s="80"/>
-      <c r="F58" s="80"/>
-      <c r="G58" s="80"/>
-      <c r="H58" s="237">
-        <v>24990</v>
-      </c>
-      <c r="I58" s="60"/>
-    </row>
-    <row r="59" spans="1:11" s="6" customFormat="1">
-      <c r="A59" s="80" t="s">
-        <v>74</v>
-      </c>
-      <c r="B59" s="80"/>
-      <c r="C59" s="80"/>
-      <c r="D59" s="80"/>
-      <c r="E59" s="80"/>
-      <c r="F59" s="80"/>
-      <c r="G59" s="80"/>
-      <c r="H59" s="69">
-        <f>SUM(H58)</f>
-        <v>24990</v>
-      </c>
-    </row>
-    <row r="60" spans="1:11" s="6" customFormat="1">
-      <c r="A60" s="210" t="s">
-        <v>135</v>
-      </c>
-      <c r="B60" s="210"/>
-      <c r="C60" s="210"/>
-      <c r="D60" s="210"/>
-      <c r="E60" s="210"/>
-      <c r="F60" s="210"/>
-      <c r="G60" s="210"/>
-      <c r="H60" s="210"/>
-    </row>
-    <row r="61" spans="1:11" s="6" customFormat="1">
-      <c r="A61" s="80"/>
-      <c r="B61" s="80"/>
-      <c r="C61" s="80"/>
-      <c r="D61" s="80"/>
-      <c r="E61" s="80"/>
-      <c r="F61" s="80"/>
-      <c r="G61" s="80"/>
-      <c r="H61" s="73"/>
-    </row>
-    <row r="62" spans="1:11" s="6" customFormat="1">
-      <c r="A62" s="80"/>
-      <c r="B62" s="80"/>
-      <c r="C62" s="80"/>
-      <c r="D62" s="80"/>
-      <c r="E62" s="80"/>
-      <c r="F62" s="80"/>
-      <c r="G62" s="80"/>
-      <c r="H62" s="73"/>
-    </row>
-    <row r="63" spans="1:11" s="6" customFormat="1">
-      <c r="A63" s="175"/>
-      <c r="B63" s="175"/>
-      <c r="C63" s="175"/>
-      <c r="D63" s="175"/>
-      <c r="E63" s="175"/>
-      <c r="F63" s="175"/>
-      <c r="G63" s="175"/>
-      <c r="H63" s="174">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="1:11" s="6" customFormat="1" ht="21" customHeight="1">
-      <c r="A64" s="80" t="s">
-        <v>75</v>
-      </c>
-      <c r="B64" s="80"/>
-      <c r="C64" s="80"/>
-      <c r="D64" s="80"/>
-      <c r="E64" s="80"/>
-      <c r="F64" s="80"/>
-      <c r="G64" s="80"/>
-      <c r="H64" s="69">
-        <f>SUM(H61:H63)</f>
-        <v>0</v>
-      </c>
-      <c r="I64" s="60"/>
-    </row>
-    <row r="65" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1">
-      <c r="A65" s="211"/>
-      <c r="B65" s="212"/>
-      <c r="C65" s="212"/>
-      <c r="D65" s="212"/>
-      <c r="E65" s="212"/>
-      <c r="F65" s="212"/>
-      <c r="G65" s="212"/>
-      <c r="H65" s="213"/>
-    </row>
-    <row r="66" spans="1:11" s="6" customFormat="1" ht="23.25" hidden="1" customHeight="1">
-      <c r="A66" s="81"/>
-      <c r="B66" s="82"/>
-      <c r="C66" s="82"/>
-      <c r="D66" s="82"/>
-      <c r="E66" s="82"/>
-      <c r="F66" s="82"/>
-      <c r="G66" s="82"/>
-      <c r="H66" s="158">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="1:11" s="6" customFormat="1" ht="20.25" hidden="1" customHeight="1">
-      <c r="A67" s="159"/>
-      <c r="B67" s="160"/>
-      <c r="C67" s="160"/>
-      <c r="D67" s="160"/>
-      <c r="E67" s="160"/>
-      <c r="F67" s="160"/>
-      <c r="G67" s="160"/>
-      <c r="H67" s="161">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" spans="1:11" s="6" customFormat="1" ht="18" hidden="1" customHeight="1">
-      <c r="A68" s="162"/>
-      <c r="B68" s="163"/>
-      <c r="C68" s="163"/>
-      <c r="D68" s="163"/>
-      <c r="E68" s="163"/>
-      <c r="F68" s="163"/>
-      <c r="G68" s="163"/>
-      <c r="H68" s="158">
-        <f>H66+H67</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" spans="1:11" s="6" customFormat="1" ht="18" hidden="1" customHeight="1">
-      <c r="A69" s="219" t="s">
-        <v>81</v>
-      </c>
-      <c r="B69" s="220"/>
-      <c r="C69" s="220"/>
-      <c r="D69" s="220"/>
-      <c r="E69" s="220"/>
-      <c r="F69" s="220"/>
-      <c r="G69" s="220"/>
-      <c r="H69" s="164">
-        <f>H64</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1">
-      <c r="A70" s="187"/>
-      <c r="B70" s="187"/>
-      <c r="C70" s="187"/>
-      <c r="D70" s="187"/>
-      <c r="E70" s="187"/>
-      <c r="F70" s="187"/>
-      <c r="G70" s="187"/>
-      <c r="H70" s="187"/>
-    </row>
-    <row r="71" spans="1:11" s="6" customFormat="1" ht="86.25" hidden="1" customHeight="1">
-      <c r="A71" s="188"/>
-      <c r="B71" s="188"/>
-      <c r="C71" s="188"/>
-      <c r="D71" s="188"/>
-      <c r="E71" s="188"/>
-      <c r="F71" s="188"/>
-      <c r="G71" s="188"/>
-      <c r="H71" s="188"/>
-    </row>
-    <row r="72" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1">
-      <c r="A72" s="221" t="s">
-        <v>83</v>
-      </c>
-      <c r="B72" s="221"/>
-      <c r="C72" s="221"/>
-      <c r="D72" s="221"/>
-      <c r="E72" s="221"/>
-      <c r="F72" s="221"/>
-      <c r="G72" s="221"/>
-      <c r="H72" s="165"/>
-    </row>
-    <row r="73" spans="1:11" s="6" customFormat="1" ht="26.25" customHeight="1">
-      <c r="A73" s="198"/>
-      <c r="B73" s="199"/>
-      <c r="C73" s="199"/>
-      <c r="D73" s="199"/>
-      <c r="E73" s="199"/>
-      <c r="F73" s="199"/>
-      <c r="G73" s="200"/>
-      <c r="H73" s="73"/>
-    </row>
-    <row r="74" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1">
-      <c r="A74" s="129" t="s">
-        <v>74</v>
-      </c>
-      <c r="B74" s="80"/>
-      <c r="C74" s="80"/>
-      <c r="D74" s="80"/>
-      <c r="E74" s="80"/>
-      <c r="F74" s="80"/>
-      <c r="G74" s="80"/>
-      <c r="H74" s="69">
-        <f>SUM(H73:H73)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1" thickBot="1">
-      <c r="A75" s="130"/>
-      <c r="B75" s="130"/>
-      <c r="C75" s="130"/>
-      <c r="D75" s="130"/>
-      <c r="E75" s="130"/>
-      <c r="F75" s="130"/>
-      <c r="G75" s="130"/>
-      <c r="H75" s="131"/>
-    </row>
-    <row r="76" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1" thickBot="1">
-      <c r="A76" s="206" t="s">
-        <v>82</v>
-      </c>
-      <c r="B76" s="207"/>
-      <c r="C76" s="207"/>
-      <c r="D76" s="207"/>
-      <c r="E76" s="207"/>
-      <c r="F76" s="207"/>
-      <c r="G76" s="207"/>
-      <c r="H76" s="132">
-        <f>H74</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1" thickBot="1">
-      <c r="A77" s="193" t="s">
-        <v>88</v>
-      </c>
-      <c r="B77" s="194"/>
-      <c r="C77" s="194"/>
-      <c r="D77" s="194"/>
-      <c r="E77" s="194"/>
-      <c r="F77" s="194"/>
-      <c r="G77" s="195"/>
-      <c r="H77" s="132"/>
-    </row>
-    <row r="78" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1" thickBot="1">
-      <c r="A78" s="193" t="s">
-        <v>93</v>
-      </c>
-      <c r="B78" s="194"/>
-      <c r="C78" s="194"/>
-      <c r="D78" s="194"/>
-      <c r="E78" s="194"/>
-      <c r="F78" s="194"/>
-      <c r="G78" s="195"/>
-      <c r="H78" s="132"/>
-    </row>
-    <row r="79" spans="1:11" ht="18">
-      <c r="A79" s="206" t="s">
-        <v>89</v>
-      </c>
-      <c r="B79" s="207"/>
-      <c r="C79" s="207"/>
-      <c r="D79" s="207"/>
-      <c r="E79" s="207"/>
-      <c r="F79" s="207"/>
-      <c r="G79" s="207"/>
-      <c r="H79" s="132">
-        <f>H29+H38+H51+H56+H59+H34+H21+H25</f>
-        <v>4388237.17</v>
-      </c>
-      <c r="J79" s="173"/>
-      <c r="K79" s="144"/>
-    </row>
-    <row r="80" spans="1:11" ht="18">
-      <c r="A80" s="214" t="s">
-        <v>122</v>
-      </c>
-      <c r="B80" s="215"/>
-      <c r="C80" s="215"/>
-      <c r="D80" s="215"/>
-      <c r="E80" s="215"/>
-      <c r="F80" s="215"/>
-      <c r="G80" s="216"/>
-      <c r="H80" s="133">
-        <f>H77+H79</f>
-        <v>4388237.17</v>
-      </c>
-      <c r="I80" s="128"/>
-      <c r="J80" s="222"/>
-      <c r="K80" s="222"/>
-    </row>
-    <row r="81" spans="1:11" ht="18">
-      <c r="A81" s="214" t="s">
-        <v>94</v>
-      </c>
-      <c r="B81" s="215"/>
-      <c r="C81" s="215"/>
-      <c r="D81" s="215"/>
-      <c r="E81" s="215"/>
-      <c r="F81" s="215"/>
-      <c r="G81" s="216"/>
-      <c r="H81" s="134">
-        <f>H78+H76</f>
-        <v>0</v>
-      </c>
-      <c r="J81" s="144"/>
-    </row>
-    <row r="82" spans="1:11" ht="20.25" customHeight="1" thickBot="1">
-      <c r="A82" s="217" t="s">
-        <v>84</v>
-      </c>
-      <c r="B82" s="218"/>
-      <c r="C82" s="218"/>
-      <c r="D82" s="218"/>
-      <c r="E82" s="218"/>
-      <c r="F82" s="218"/>
-      <c r="G82" s="218"/>
-      <c r="H82" s="135">
-        <f>H79+H76</f>
-        <v>4388237.17</v>
-      </c>
-      <c r="J82" s="7"/>
-    </row>
-    <row r="83" spans="1:11" ht="18" hidden="1">
-      <c r="A83" s="208" t="s">
-        <v>17</v>
-      </c>
-      <c r="B83" s="209"/>
-      <c r="C83" s="209"/>
-      <c r="D83" s="209"/>
-      <c r="E83" s="209"/>
-      <c r="F83" s="209"/>
-      <c r="G83" s="209"/>
-      <c r="H83" s="136">
-        <f>H68</f>
-        <v>0</v>
-      </c>
-      <c r="J83" s="7"/>
-    </row>
-    <row r="84" spans="1:11" ht="18" hidden="1">
-      <c r="A84" s="137"/>
-      <c r="B84" s="137"/>
-      <c r="C84" s="137"/>
-      <c r="D84" s="137"/>
-      <c r="E84" s="137"/>
-      <c r="F84" s="137"/>
-      <c r="G84" s="137"/>
-      <c r="H84" s="138"/>
-      <c r="J84" s="7"/>
-    </row>
-    <row r="85" spans="1:11" ht="18" hidden="1">
-      <c r="A85" s="137"/>
-      <c r="B85" s="137"/>
-      <c r="C85" s="137"/>
-      <c r="D85" s="137"/>
-      <c r="E85" s="137"/>
-      <c r="F85" s="137"/>
-      <c r="G85" s="137"/>
-      <c r="H85" s="138"/>
-      <c r="J85" s="7"/>
-    </row>
-    <row r="86" spans="1:11" ht="18" hidden="1">
-      <c r="A86" s="137"/>
-      <c r="B86" s="137"/>
-      <c r="C86" s="137"/>
-      <c r="D86" s="137"/>
-      <c r="E86" s="137"/>
-      <c r="F86" s="137"/>
-      <c r="G86" s="137"/>
-      <c r="H86" s="138"/>
-      <c r="J86" s="7"/>
-    </row>
-    <row r="87" spans="1:11" ht="14.25" customHeight="1">
-      <c r="A87" s="139"/>
-      <c r="B87" s="139"/>
-      <c r="C87" s="139"/>
-      <c r="D87" s="139"/>
-      <c r="E87" s="139"/>
-      <c r="F87" s="139"/>
-      <c r="G87" s="139"/>
-      <c r="H87" s="139"/>
-    </row>
-    <row r="88" spans="1:11" ht="18">
-      <c r="A88" s="226" t="s">
-        <v>10</v>
-      </c>
-      <c r="B88" s="227"/>
-      <c r="C88" s="227"/>
-      <c r="D88" s="227"/>
-      <c r="E88" s="227"/>
-      <c r="F88" s="227"/>
-      <c r="G88" s="227"/>
-      <c r="H88" s="228"/>
-    </row>
-    <row r="89" spans="1:11" ht="18">
-      <c r="A89" s="140" t="s">
-        <v>12</v>
-      </c>
-      <c r="B89" s="141"/>
-      <c r="C89" s="141"/>
-      <c r="D89" s="141"/>
-      <c r="E89" s="141"/>
-      <c r="F89" s="141"/>
-      <c r="G89" s="141"/>
-      <c r="H89" s="142">
-        <v>4176361.2016003644</v>
-      </c>
-    </row>
-    <row r="90" spans="1:11">
-      <c r="A90" s="81" t="s">
-        <v>129</v>
-      </c>
-      <c r="B90" s="82"/>
-      <c r="C90" s="82"/>
-      <c r="D90" s="82"/>
-      <c r="E90" s="82"/>
-      <c r="F90" s="82"/>
-      <c r="G90" s="82"/>
-      <c r="H90" s="143">
-        <f>Planilla!G32</f>
-        <v>3671141.4911220977</v>
-      </c>
-    </row>
-    <row r="91" spans="1:11">
-      <c r="A91" s="78" t="s">
-        <v>163</v>
-      </c>
-      <c r="B91" s="79"/>
-      <c r="C91" s="79"/>
-      <c r="D91" s="79"/>
-      <c r="E91" s="79"/>
-      <c r="F91" s="79"/>
-      <c r="G91" s="79"/>
-      <c r="H91" s="183">
-        <f>-(H82)</f>
-        <v>-4388237.17</v>
-      </c>
-    </row>
-    <row r="92" spans="1:11">
-      <c r="A92" s="78" t="s">
-        <v>85</v>
-      </c>
-      <c r="B92" s="79"/>
-      <c r="C92" s="79"/>
-      <c r="D92" s="79"/>
-      <c r="E92" s="79"/>
-      <c r="F92" s="79"/>
-      <c r="G92" s="79"/>
-      <c r="H92" s="183">
-        <f>-H69</f>
-        <v>0</v>
-      </c>
-      <c r="K92" s="6"/>
+      <c r="B92" s="91"/>
+      <c r="C92" s="4"/>
+      <c r="D92" s="61"/>
+      <c r="E92" s="61"/>
+      <c r="F92" s="61"/>
+      <c r="G92" s="61"/>
+      <c r="H92" s="126"/>
     </row>
     <row r="93" spans="1:11">
-      <c r="A93" s="78" t="s">
-        <v>72</v>
-      </c>
-      <c r="B93" s="79" t="s">
-        <v>114</v>
-      </c>
-      <c r="C93" s="79"/>
-      <c r="D93" s="79"/>
-      <c r="E93" s="79"/>
-      <c r="F93" s="79"/>
-      <c r="G93" s="79"/>
-      <c r="H93" s="123">
-        <v>133680</v>
-      </c>
+      <c r="A93" s="61"/>
+      <c r="B93" s="97"/>
+      <c r="C93" s="61"/>
+      <c r="D93" s="61"/>
+      <c r="E93" s="61"/>
+      <c r="F93" s="61"/>
+      <c r="G93" s="61"/>
+      <c r="H93" s="21"/>
     </row>
     <row r="94" spans="1:11">
-      <c r="A94" s="78" t="s">
-        <v>71</v>
-      </c>
-      <c r="B94" s="79"/>
-      <c r="C94" s="79"/>
-      <c r="D94" s="79"/>
-      <c r="E94" s="79"/>
-      <c r="F94" s="79"/>
-      <c r="G94" s="79"/>
-      <c r="H94" s="123">
-        <f>180000-H93</f>
-        <v>46320</v>
-      </c>
-      <c r="I94" s="144"/>
+      <c r="A94" s="61"/>
+      <c r="B94" s="61"/>
+      <c r="C94" s="61"/>
+      <c r="D94" s="61"/>
+      <c r="E94" s="61"/>
+      <c r="F94" s="61"/>
+      <c r="G94" s="61"/>
+      <c r="H94" s="21"/>
     </row>
     <row r="95" spans="1:11">
-      <c r="A95" s="12" t="s">
-        <v>120</v>
-      </c>
-      <c r="B95" s="83"/>
-      <c r="C95" s="4"/>
-      <c r="D95" s="4"/>
-      <c r="E95" s="4"/>
-      <c r="F95" s="4"/>
-      <c r="G95" s="4"/>
-      <c r="H95" s="98"/>
-    </row>
-    <row r="96" spans="1:11" ht="18">
-      <c r="A96" s="22" t="s">
+      <c r="A95" s="85" t="s">
         <v>11</v>
       </c>
-      <c r="B96" s="23"/>
-      <c r="C96" s="23"/>
-      <c r="D96" s="23"/>
-      <c r="E96" s="23"/>
-      <c r="F96" s="23"/>
-      <c r="G96" s="23"/>
-      <c r="H96" s="84">
-        <f>SUM(H89:H95)</f>
-        <v>3639265.5227224622</v>
-      </c>
-    </row>
-    <row r="97" spans="1:8" ht="15" thickBot="1"/>
-    <row r="98" spans="1:8" ht="16.2" thickBot="1">
-      <c r="A98" s="223" t="s">
-        <v>98</v>
-      </c>
-      <c r="B98" s="224"/>
-      <c r="C98" s="224"/>
-      <c r="D98" s="224"/>
-      <c r="E98" s="224"/>
-      <c r="F98" s="224"/>
-      <c r="G98" s="224"/>
-      <c r="H98" s="225"/>
-    </row>
-    <row r="99" spans="1:8" ht="15.6">
-      <c r="A99" s="87" t="s">
-        <v>12</v>
-      </c>
-      <c r="B99" s="87"/>
-      <c r="C99" s="87"/>
-      <c r="D99" s="87"/>
-      <c r="E99" s="87"/>
-      <c r="F99" s="87"/>
-      <c r="G99" s="87"/>
-      <c r="H99" s="88">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="100" spans="1:8">
-      <c r="A100" s="61" t="s">
-        <v>121</v>
-      </c>
-      <c r="B100" s="91"/>
-      <c r="C100" s="4"/>
-      <c r="D100" s="61"/>
-      <c r="E100" s="61"/>
-      <c r="F100" s="61"/>
-      <c r="G100" s="61"/>
-      <c r="H100" s="127"/>
-    </row>
-    <row r="101" spans="1:8">
-      <c r="A101" s="61"/>
-      <c r="B101" s="97"/>
-      <c r="C101" s="61"/>
-      <c r="D101" s="61"/>
-      <c r="E101" s="61"/>
-      <c r="F101" s="61"/>
-      <c r="G101" s="61"/>
-      <c r="H101" s="21"/>
-    </row>
-    <row r="102" spans="1:8">
-      <c r="A102" s="61"/>
-      <c r="B102" s="61"/>
-      <c r="C102" s="61"/>
-      <c r="D102" s="61"/>
-      <c r="E102" s="61"/>
-      <c r="F102" s="61"/>
-      <c r="G102" s="61"/>
-      <c r="H102" s="21"/>
-    </row>
-    <row r="103" spans="1:8">
-      <c r="A103" s="85" t="s">
-        <v>11</v>
-      </c>
-      <c r="B103" s="85"/>
-      <c r="C103" s="85"/>
-      <c r="D103" s="85"/>
-      <c r="E103" s="85"/>
-      <c r="F103" s="85"/>
-      <c r="G103" s="85"/>
-      <c r="H103" s="86">
-        <f>SUM(H99:H102)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="106" spans="1:8" hidden="1">
-      <c r="A106" s="202"/>
-      <c r="B106" s="202"/>
-      <c r="C106" s="202"/>
-      <c r="D106" s="202"/>
-      <c r="E106" s="202"/>
-      <c r="F106" s="202"/>
-      <c r="G106" s="202"/>
-      <c r="H106" s="202"/>
-    </row>
-    <row r="107" spans="1:8" hidden="1">
-      <c r="A107" s="202"/>
-      <c r="B107" s="202"/>
-      <c r="C107" s="202"/>
-      <c r="D107" s="202"/>
-      <c r="E107" s="202"/>
-      <c r="F107" s="202"/>
-      <c r="G107" s="202"/>
-      <c r="H107" s="202"/>
-    </row>
-    <row r="108" spans="1:8" hidden="1">
-      <c r="A108" s="202"/>
-      <c r="B108" s="202"/>
-      <c r="C108" s="202"/>
-      <c r="D108" s="202"/>
-      <c r="E108" s="202"/>
-      <c r="F108" s="202"/>
-      <c r="G108" s="202"/>
-      <c r="H108" s="202"/>
-    </row>
-    <row r="109" spans="1:8" hidden="1">
-      <c r="A109" s="202"/>
-      <c r="B109" s="202"/>
-      <c r="C109" s="202"/>
-      <c r="D109" s="202"/>
-      <c r="E109" s="202"/>
-      <c r="F109" s="202"/>
-      <c r="G109" s="202"/>
-      <c r="H109" s="202"/>
+      <c r="B95" s="85"/>
+      <c r="C95" s="85"/>
+      <c r="D95" s="85"/>
+      <c r="E95" s="85"/>
+      <c r="F95" s="85"/>
+      <c r="G95" s="85"/>
+      <c r="H95" s="86">
+        <f>SUM(H91:H94)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" hidden="1">
+      <c r="A98" s="187"/>
+      <c r="B98" s="187"/>
+      <c r="C98" s="187"/>
+      <c r="D98" s="187"/>
+      <c r="E98" s="187"/>
+      <c r="F98" s="187"/>
+      <c r="G98" s="187"/>
+      <c r="H98" s="187"/>
+    </row>
+    <row r="99" spans="1:8" hidden="1">
+      <c r="A99" s="187"/>
+      <c r="B99" s="187"/>
+      <c r="C99" s="187"/>
+      <c r="D99" s="187"/>
+      <c r="E99" s="187"/>
+      <c r="F99" s="187"/>
+      <c r="G99" s="187"/>
+      <c r="H99" s="187"/>
+    </row>
+    <row r="100" spans="1:8" hidden="1">
+      <c r="A100" s="187"/>
+      <c r="B100" s="187"/>
+      <c r="C100" s="187"/>
+      <c r="D100" s="187"/>
+      <c r="E100" s="187"/>
+      <c r="F100" s="187"/>
+      <c r="G100" s="187"/>
+      <c r="H100" s="187"/>
+    </row>
+    <row r="101" spans="1:8" hidden="1">
+      <c r="A101" s="187"/>
+      <c r="B101" s="187"/>
+      <c r="C101" s="187"/>
+      <c r="D101" s="187"/>
+      <c r="E101" s="187"/>
+      <c r="F101" s="187"/>
+      <c r="G101" s="187"/>
+      <c r="H101" s="187"/>
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="J80:K80"/>
-    <mergeCell ref="A106:H109"/>
-    <mergeCell ref="A98:H98"/>
-    <mergeCell ref="A88:H88"/>
-    <mergeCell ref="A79:G79"/>
-    <mergeCell ref="A83:G83"/>
-    <mergeCell ref="A14:H14"/>
-    <mergeCell ref="A35:H35"/>
-    <mergeCell ref="A39:H39"/>
+    <mergeCell ref="D2:H2"/>
+    <mergeCell ref="A27:H27"/>
+    <mergeCell ref="A70:G70"/>
+    <mergeCell ref="A23:H23"/>
+    <mergeCell ref="A19:H19"/>
+    <mergeCell ref="A65:G65"/>
+    <mergeCell ref="A12:H12"/>
+    <mergeCell ref="E3:H3"/>
     <mergeCell ref="A52:H52"/>
     <mergeCell ref="A57:H57"/>
-    <mergeCell ref="A60:H60"/>
-    <mergeCell ref="A65:H65"/>
-    <mergeCell ref="A81:G81"/>
-    <mergeCell ref="A77:G77"/>
-    <mergeCell ref="A80:G80"/>
-    <mergeCell ref="A82:G82"/>
+    <mergeCell ref="A73:G73"/>
     <mergeCell ref="A69:G69"/>
-    <mergeCell ref="A76:G76"/>
     <mergeCell ref="A72:G72"/>
-    <mergeCell ref="A70:H71"/>
-    <mergeCell ref="D2:H2"/>
-    <mergeCell ref="A30:H30"/>
-    <mergeCell ref="A78:G78"/>
-    <mergeCell ref="A26:H26"/>
-    <mergeCell ref="A22:H22"/>
-    <mergeCell ref="A73:G73"/>
-    <mergeCell ref="A12:H12"/>
-    <mergeCell ref="E3:H3"/>
+    <mergeCell ref="A61:G61"/>
+    <mergeCell ref="A68:G68"/>
+    <mergeCell ref="A64:G64"/>
+    <mergeCell ref="A62:H63"/>
+    <mergeCell ref="A14:H14"/>
+    <mergeCell ref="A32:H32"/>
+    <mergeCell ref="A36:H36"/>
+    <mergeCell ref="A45:H45"/>
+    <mergeCell ref="A49:H49"/>
+    <mergeCell ref="J72:K72"/>
+    <mergeCell ref="A98:H101"/>
+    <mergeCell ref="A90:H90"/>
+    <mergeCell ref="A80:H80"/>
+    <mergeCell ref="A71:G71"/>
+    <mergeCell ref="A75:G75"/>
+    <mergeCell ref="A74:G74"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="85" orientation="landscape" r:id="rId1"/>
@@ -3661,7 +3540,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q41"/>
+  <dimension ref="A1:R41"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="4.5546875" customWidth="1"/>
@@ -3674,11 +3553,12 @@
     <col min="9" max="9" width="12.5546875" style="2" customWidth="1"/>
     <col min="10" max="10" width="11" style="2" customWidth="1"/>
     <col min="11" max="11" width="10.5546875" style="2" customWidth="1"/>
-    <col min="12" max="12" width="14.5546875" customWidth="1"/>
-    <col min="13" max="13" width="13.44140625" customWidth="1"/>
-    <col min="14" max="14" width="15.109375" customWidth="1"/>
-    <col min="15" max="15" width="12" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="18.21875" style="2" customWidth="1"/>
+    <col min="13" max="13" width="14.5546875" customWidth="1"/>
+    <col min="14" max="14" width="13.44140625" customWidth="1"/>
+    <col min="15" max="15" width="15.109375" customWidth="1"/>
+    <col min="16" max="16" width="12" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="26.25" customHeight="1">
@@ -3703,13 +3583,14 @@
       <c r="K1" s="103"/>
       <c r="L1" s="103"/>
       <c r="M1" s="103"/>
-      <c r="N1" s="107"/>
+      <c r="N1" s="103"/>
+      <c r="O1" s="107"/>
     </row>
     <row r="2" spans="1:17">
       <c r="A2" s="61"/>
       <c r="B2" s="61"/>
-      <c r="C2" s="126">
-        <v>1333150</v>
+      <c r="C2" s="125">
+        <v>1310527.79</v>
       </c>
       <c r="D2" s="61"/>
       <c r="E2" s="61"/>
@@ -3719,15 +3600,16 @@
       <c r="I2" s="114"/>
       <c r="J2" s="114"/>
       <c r="K2" s="114"/>
-      <c r="L2" s="61"/>
+      <c r="L2" s="114"/>
       <c r="M2" s="61"/>
       <c r="N2" s="61"/>
+      <c r="O2" s="61"/>
     </row>
     <row r="3" spans="1:17">
       <c r="A3" s="115"/>
       <c r="B3" s="116"/>
       <c r="C3" s="101">
-        <v>2782455.8899999997</v>
+        <v>4081947.54</v>
       </c>
       <c r="D3" s="61"/>
       <c r="E3" s="61"/>
@@ -3737,90 +3619,100 @@
       <c r="I3" s="117"/>
       <c r="J3" s="117"/>
       <c r="K3" s="117"/>
-      <c r="L3" s="61" t="s">
-        <v>78</v>
-      </c>
-      <c r="M3" s="61"/>
+      <c r="L3" s="117"/>
+      <c r="M3" s="61" t="s">
+        <v>77</v>
+      </c>
       <c r="N3" s="61"/>
+      <c r="O3" s="61"/>
     </row>
     <row r="4" spans="1:17" ht="18.75" customHeight="1">
       <c r="A4" s="118"/>
       <c r="B4" s="119" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="C4" s="61"/>
       <c r="D4" s="61"/>
       <c r="E4" s="119" t="s">
-        <v>80</v>
-      </c>
-      <c r="F4" s="122"/>
+        <v>79</v>
+      </c>
+      <c r="F4" s="121"/>
       <c r="G4" s="117"/>
       <c r="H4" s="117"/>
       <c r="I4" s="117"/>
       <c r="J4" s="117"/>
       <c r="K4" s="117"/>
-      <c r="L4" s="61" t="s">
-        <v>77</v>
-      </c>
-      <c r="M4" s="61"/>
+      <c r="L4" s="117"/>
+      <c r="M4" s="61" t="s">
+        <v>76</v>
+      </c>
       <c r="N4" s="61"/>
+      <c r="O4" s="61"/>
     </row>
     <row r="5" spans="1:17" ht="15.75" customHeight="1">
       <c r="A5" s="120"/>
-      <c r="B5" s="230">
-        <f>C3</f>
-        <v>2782455.8899999997</v>
-      </c>
-      <c r="C5" s="230"/>
+      <c r="B5" s="229">
+        <f>C3-B7</f>
+        <v>2771419.75</v>
+      </c>
+      <c r="C5" s="229"/>
       <c r="D5" s="21"/>
-      <c r="E5" s="121">
+      <c r="E5" s="239">
         <v>70000</v>
       </c>
-      <c r="F5" s="114"/>
+      <c r="F5" s="240"/>
       <c r="G5" s="114"/>
       <c r="H5" s="114"/>
       <c r="I5" s="114"/>
       <c r="J5" s="114"/>
       <c r="K5" s="114"/>
-      <c r="L5" s="61"/>
+      <c r="L5" s="114"/>
       <c r="M5" s="61"/>
       <c r="N5" s="61"/>
+      <c r="O5" s="61"/>
     </row>
     <row r="6" spans="1:17" ht="15.75" customHeight="1">
       <c r="A6" s="120"/>
-      <c r="B6" s="232" t="s">
-        <v>150</v>
-      </c>
-      <c r="C6" s="233"/>
+      <c r="B6" s="231" t="s">
+        <v>145</v>
+      </c>
+      <c r="C6" s="232"/>
       <c r="D6" s="21"/>
-      <c r="E6" s="119"/>
-      <c r="F6" s="114"/>
+      <c r="E6" s="231" t="s">
+        <v>159</v>
+      </c>
+      <c r="F6" s="232"/>
       <c r="G6" s="114"/>
       <c r="H6" s="114"/>
       <c r="I6" s="114"/>
       <c r="J6" s="114"/>
       <c r="K6" s="114"/>
-      <c r="L6" s="61"/>
+      <c r="L6" s="114"/>
       <c r="M6" s="61"/>
       <c r="N6" s="61"/>
+      <c r="O6" s="61"/>
     </row>
     <row r="7" spans="1:17" ht="18.75" customHeight="1">
       <c r="A7" s="120"/>
-      <c r="B7" s="230">
-        <v>2000000</v>
-      </c>
-      <c r="C7" s="230"/>
+      <c r="B7" s="229">
+        <f>C2</f>
+        <v>1310527.79</v>
+      </c>
+      <c r="C7" s="229"/>
       <c r="D7" s="21"/>
-      <c r="E7" s="21"/>
-      <c r="F7" s="114"/>
+      <c r="E7" s="237">
+        <v>1000000</v>
+      </c>
+      <c r="F7" s="238"/>
       <c r="G7" s="114"/>
       <c r="H7" s="114"/>
       <c r="I7" s="114"/>
       <c r="J7" s="114"/>
       <c r="K7" s="114"/>
-      <c r="L7" s="61"/>
+      <c r="L7" s="114"/>
       <c r="M7" s="61"/>
       <c r="N7" s="61"/>
+      <c r="O7" s="61"/>
     </row>
     <row r="8" spans="1:17" ht="53.25" customHeight="1" thickBot="1">
       <c r="A8" s="108" t="s">
@@ -3833,7 +3725,7 @@
         <v>1</v>
       </c>
       <c r="D8" s="111" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E8" s="109" t="s">
         <v>2</v>
@@ -3842,52 +3734,55 @@
         <v>16</v>
       </c>
       <c r="G8" s="112" t="s">
-        <v>159</v>
+        <v>148</v>
       </c>
       <c r="H8" s="112" t="s">
         <v>63</v>
       </c>
       <c r="I8" s="112" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="J8" s="112" t="s">
         <v>64</v>
       </c>
-      <c r="K8" s="125" t="s">
-        <v>127</v>
+      <c r="K8" s="124" t="s">
+        <v>125</v>
       </c>
       <c r="L8" s="109" t="s">
+        <v>82</v>
+      </c>
+      <c r="M8" s="109" t="s">
         <v>7</v>
       </c>
-      <c r="M8" s="109" t="s">
-        <v>145</v>
-      </c>
-      <c r="N8" s="113" t="s">
+      <c r="N8" s="109" t="s">
+        <v>142</v>
+      </c>
+      <c r="O8" s="113" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:17" ht="15" customHeight="1">
-      <c r="A9" s="171">
+      <c r="A9" s="170">
         <v>1</v>
       </c>
-      <c r="B9" s="167" t="s">
+      <c r="B9" s="166" t="s">
         <v>40</v>
       </c>
-      <c r="C9" s="168" t="s">
+      <c r="C9" s="167" t="s">
         <v>19</v>
       </c>
-      <c r="D9" s="168" t="s">
-        <v>102</v>
-      </c>
-      <c r="E9" s="169">
+      <c r="D9" s="167" t="s">
+        <v>101</v>
+      </c>
+      <c r="E9" s="168">
         <v>4.0500000000000001E-2</v>
       </c>
       <c r="F9" s="98">
-        <v>176411.92014</v>
-      </c>
-      <c r="G9" s="180">
+        <v>193689.46354500001</v>
+      </c>
+      <c r="G9" s="179">
         <f>F9</f>
-        <v>176411.92014</v>
+        <v>193689.46354500001</v>
       </c>
       <c r="H9" s="68">
         <f>IF(F9&gt;G9,F9-G9,0)</f>
@@ -3905,17 +3800,21 @@
         <f>F$4*E9</f>
         <v>0</v>
       </c>
-      <c r="L9" s="170">
+      <c r="L9" s="68">
+        <f>E$7*E9</f>
+        <v>40500</v>
+      </c>
+      <c r="M9" s="169">
         <f>B$5*E9</f>
-        <v>112689.46354499999</v>
-      </c>
-      <c r="M9" s="170">
+        <v>112242.49987500001</v>
+      </c>
+      <c r="N9" s="169">
         <f>B$7*E9</f>
-        <v>81000</v>
-      </c>
-      <c r="N9" s="170">
-        <f>H9+I9-J9+K9+L9+M9</f>
-        <v>193689.46354500001</v>
+        <v>53076.375495</v>
+      </c>
+      <c r="O9" s="241">
+        <f>H9+I9-J9+K9+M9+N9+L9</f>
+        <v>205818.87537000002</v>
       </c>
     </row>
     <row r="10" spans="1:17" ht="15" customHeight="1">
@@ -3933,11 +3832,11 @@
         <v>6.4799999999999996E-2</v>
       </c>
       <c r="F10" s="17">
-        <v>282259.072224</v>
-      </c>
-      <c r="G10" s="180">
+        <v>309903.14167199994</v>
+      </c>
+      <c r="G10" s="179">
         <f>F10</f>
-        <v>282259.072224</v>
+        <v>309903.14167199994</v>
       </c>
       <c r="H10" s="24">
         <f t="shared" ref="H10:H31" si="0">IF(F10&gt;G10,F10-G10,0)</f>
@@ -3955,48 +3854,52 @@
         <f t="shared" ref="K10:K31" si="2">F$4*E10</f>
         <v>0</v>
       </c>
-      <c r="L10" s="25">
-        <f t="shared" ref="L10:L31" si="3">B$5*E10</f>
-        <v>180303.14167199997</v>
+      <c r="L10" s="68">
+        <f t="shared" ref="L10:L31" si="3">E$7*E10</f>
+        <v>64800</v>
       </c>
       <c r="M10" s="25">
-        <f t="shared" ref="M10:M31" si="4">B$7*E10</f>
-        <v>129600</v>
+        <f t="shared" ref="M10:M31" si="4">B$5*E10</f>
+        <v>179587.99979999999</v>
       </c>
       <c r="N10" s="25">
-        <f t="shared" ref="N10:N31" si="5">H10+I10-J10+K10+L10+M10</f>
-        <v>309903.14167199994</v>
+        <f t="shared" ref="N10:N31" si="5">B$7*E10</f>
+        <v>84922.200792000003</v>
+      </c>
+      <c r="O10" s="241">
+        <f t="shared" ref="O10:O31" si="6">H10+I10-J10+K10+M10+N10+L10</f>
+        <v>329310.20059199998</v>
       </c>
     </row>
     <row r="11" spans="1:17" ht="15" customHeight="1">
-      <c r="A11" s="166">
+      <c r="A11" s="165">
         <v>3</v>
       </c>
-      <c r="B11" s="167" t="s">
+      <c r="B11" s="166" t="s">
         <v>42</v>
       </c>
-      <c r="C11" s="168" t="s">
+      <c r="C11" s="167" t="s">
         <v>21</v>
       </c>
-      <c r="D11" s="168" t="s">
-        <v>104</v>
-      </c>
-      <c r="E11" s="169">
+      <c r="D11" s="167" t="s">
+        <v>103</v>
+      </c>
+      <c r="E11" s="168">
         <v>4.82E-2</v>
       </c>
       <c r="F11" s="98">
-        <v>209951.96421599999</v>
-      </c>
-      <c r="G11" s="180">
+        <v>230514.37389799999</v>
+      </c>
+      <c r="G11" s="179">
         <f>F11</f>
-        <v>209951.96421599999</v>
+        <v>230514.37389799999</v>
       </c>
       <c r="H11" s="68">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I11" s="68">
-        <f t="shared" ref="I11:I31" si="6">H11*3.7%</f>
+        <f t="shared" ref="I11:I31" si="7">H11*3.7%</f>
         <v>0</v>
       </c>
       <c r="J11" s="68">
@@ -4007,66 +3910,74 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L11" s="170">
+      <c r="L11" s="68">
         <f t="shared" si="3"/>
-        <v>134114.37389799999</v>
-      </c>
-      <c r="M11" s="170">
+        <v>48200</v>
+      </c>
+      <c r="M11" s="169">
         <f t="shared" si="4"/>
-        <v>96400</v>
-      </c>
-      <c r="N11" s="170">
-        <f>H11+I11-J11+K11+L11+M11+E7</f>
-        <v>230514.37389799999</v>
+        <v>133582.43195</v>
+      </c>
+      <c r="N11" s="169">
+        <f t="shared" si="5"/>
+        <v>63167.439478</v>
+      </c>
+      <c r="O11" s="241">
+        <f t="shared" si="6"/>
+        <v>244949.87142799998</v>
       </c>
     </row>
     <row r="12" spans="1:17" ht="15" customHeight="1">
-      <c r="A12" s="145">
+      <c r="A12" s="144">
         <v>4</v>
       </c>
-      <c r="B12" s="157" t="s">
+      <c r="B12" s="156" t="s">
         <v>43</v>
       </c>
-      <c r="C12" s="155" t="s">
-        <v>100</v>
-      </c>
-      <c r="D12" s="155" t="s">
-        <v>105</v>
-      </c>
-      <c r="E12" s="156">
+      <c r="C12" s="154" t="s">
+        <v>99</v>
+      </c>
+      <c r="D12" s="154" t="s">
+        <v>104</v>
+      </c>
+      <c r="E12" s="155">
         <v>5.3499999999999999E-2</v>
       </c>
-      <c r="F12" s="149">
-        <v>3320511.6735152486</v>
-      </c>
-      <c r="G12" s="181"/>
-      <c r="H12" s="150">
+      <c r="F12" s="148">
+        <v>3699231.9955503126</v>
+      </c>
+      <c r="G12" s="180"/>
+      <c r="H12" s="149">
         <f t="shared" si="0"/>
-        <v>3320511.6735152486</v>
-      </c>
-      <c r="I12" s="150">
+        <v>3699231.9955503126</v>
+      </c>
+      <c r="I12" s="149">
+        <f t="shared" si="7"/>
+        <v>136871.58383536158</v>
+      </c>
+      <c r="J12" s="149">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K12" s="149">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L12" s="149">
+        <f t="shared" si="3"/>
+        <v>53500</v>
+      </c>
+      <c r="M12" s="150">
+        <f t="shared" si="4"/>
+        <v>148270.95662499999</v>
+      </c>
+      <c r="N12" s="150">
+        <f t="shared" si="5"/>
+        <v>70113.236764999994</v>
+      </c>
+      <c r="O12" s="242">
         <f t="shared" si="6"/>
-        <v>122858.93192006422</v>
-      </c>
-      <c r="J12" s="150">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K12" s="150">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="L12" s="151">
-        <f t="shared" si="3"/>
-        <v>148861.39011499999</v>
-      </c>
-      <c r="M12" s="151">
-        <f t="shared" si="4"/>
-        <v>107000</v>
-      </c>
-      <c r="N12" s="151">
-        <f t="shared" si="5"/>
-        <v>3699231.9955503126</v>
+        <v>4107987.7727756742</v>
       </c>
     </row>
     <row r="13" spans="1:17" ht="15" customHeight="1">
@@ -4084,18 +3995,18 @@
         <v>3.85E-2</v>
       </c>
       <c r="F13" s="17">
-        <v>167700.22038000001</v>
-      </c>
-      <c r="G13" s="180">
+        <v>184124.55176499998</v>
+      </c>
+      <c r="G13" s="179">
         <f>F13</f>
-        <v>167700.22038000001</v>
+        <v>184124.55176499998</v>
       </c>
       <c r="H13" s="24">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I13" s="24">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="J13" s="24">
@@ -4106,17 +4017,21 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L13" s="25">
+      <c r="L13" s="68">
         <f t="shared" si="3"/>
-        <v>107124.55176499998</v>
+        <v>38500</v>
       </c>
       <c r="M13" s="25">
         <f t="shared" si="4"/>
-        <v>77000</v>
+        <v>106699.66037499999</v>
       </c>
       <c r="N13" s="25">
         <f t="shared" si="5"/>
-        <v>184124.55176499998</v>
+        <v>50455.319915</v>
+      </c>
+      <c r="O13" s="241">
+        <f t="shared" si="6"/>
+        <v>195654.98028999998</v>
       </c>
     </row>
     <row r="14" spans="1:17" ht="15" customHeight="1">
@@ -4130,24 +4045,24 @@
         <v>24</v>
       </c>
       <c r="D14" s="92" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E14" s="45">
         <v>3.5900000000000001E-2</v>
       </c>
       <c r="F14" s="17">
-        <v>156375.01069199998</v>
-      </c>
-      <c r="G14" s="180">
+        <v>171690.166451</v>
+      </c>
+      <c r="G14" s="179">
         <f>F14</f>
-        <v>156375.01069199998</v>
+        <v>171690.166451</v>
       </c>
       <c r="H14" s="24">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I14" s="24">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="J14" s="24">
@@ -4158,20 +4073,21 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L14" s="25">
+      <c r="L14" s="68">
         <f t="shared" si="3"/>
-        <v>99890.166450999997</v>
+        <v>35900</v>
       </c>
       <c r="M14" s="25">
         <f t="shared" si="4"/>
-        <v>71800</v>
+        <v>99493.969024999999</v>
       </c>
       <c r="N14" s="25">
         <f t="shared" si="5"/>
-        <v>171690.166451</v>
-      </c>
-      <c r="P14" t="s">
-        <v>146</v>
+        <v>47047.947661000006</v>
+      </c>
+      <c r="O14" s="241">
+        <f t="shared" si="6"/>
+        <v>182441.91668600001</v>
       </c>
     </row>
     <row r="15" spans="1:17" ht="15" customHeight="1">
@@ -4182,27 +4098,27 @@
         <v>46</v>
       </c>
       <c r="C15" s="93" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="D15" s="92" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E15" s="45">
         <v>4.1399999999999999E-2</v>
       </c>
       <c r="F15" s="17">
-        <v>97532.185031999994</v>
-      </c>
-      <c r="G15" s="180">
+        <v>115193.67384599999</v>
+      </c>
+      <c r="G15" s="179">
         <f>F15</f>
-        <v>97532.185031999994</v>
+        <v>115193.67384599999</v>
       </c>
       <c r="H15" s="24">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I15" s="24">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="J15" s="24">
@@ -4213,23 +4129,22 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L15" s="25">
+      <c r="L15" s="68">
         <f t="shared" si="3"/>
-        <v>115193.67384599999</v>
+        <v>41400</v>
       </c>
       <c r="M15" s="25">
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>114736.77765</v>
       </c>
       <c r="N15" s="25">
-        <f t="shared" si="5"/>
-        <v>115193.67384599999</v>
-      </c>
-      <c r="P15" s="184">
-        <v>1006446</v>
-      </c>
-      <c r="Q15" t="s">
-        <v>147</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="O15" s="241">
+        <f t="shared" si="6"/>
+        <v>156136.77765</v>
+      </c>
+      <c r="Q15" s="183"/>
     </row>
     <row r="16" spans="1:17" ht="15" customHeight="1">
       <c r="A16" s="51">
@@ -4239,27 +4154,27 @@
         <v>47</v>
       </c>
       <c r="C16" s="93" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D16" s="92" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E16" s="45">
         <v>5.3499999999999999E-2</v>
       </c>
       <c r="F16" s="17">
-        <v>233037.96857999999</v>
-      </c>
-      <c r="G16" s="180">
+        <v>255861.39011499999</v>
+      </c>
+      <c r="G16" s="179">
         <f>F16</f>
-        <v>233037.96857999999</v>
+        <v>255861.39011499999</v>
       </c>
       <c r="H16" s="24">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I16" s="24">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="J16" s="24">
@@ -4270,26 +4185,25 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L16" s="25">
+      <c r="L16" s="68">
         <f t="shared" si="3"/>
-        <v>148861.39011499999</v>
+        <v>53500</v>
       </c>
       <c r="M16" s="25">
         <f t="shared" si="4"/>
-        <v>107000</v>
+        <v>148270.95662499999</v>
       </c>
       <c r="N16" s="25">
         <f t="shared" si="5"/>
-        <v>255861.39011499999</v>
-      </c>
-      <c r="P16" s="184">
-        <v>-82700</v>
-      </c>
-      <c r="Q16" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="17" spans="1:17" ht="15" customHeight="1">
+        <v>70113.236764999994</v>
+      </c>
+      <c r="O16" s="241">
+        <f t="shared" si="6"/>
+        <v>271884.19338999997</v>
+      </c>
+      <c r="Q16" s="183"/>
+    </row>
+    <row r="17" spans="1:18" ht="15" customHeight="1">
       <c r="A17" s="51">
         <v>9</v>
       </c>
@@ -4300,24 +4214,24 @@
         <v>26</v>
       </c>
       <c r="D17" s="92" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E17" s="45">
         <v>3.85E-2</v>
       </c>
       <c r="F17" s="17">
-        <v>167700.22038000001</v>
-      </c>
-      <c r="G17" s="180">
+        <v>184124.55176499998</v>
+      </c>
+      <c r="G17" s="179">
         <f>F17</f>
-        <v>167700.22038000001</v>
+        <v>184124.55176499998</v>
       </c>
       <c r="H17" s="24">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I17" s="24">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="J17" s="24">
@@ -4328,22 +4242,26 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L17" s="25">
+      <c r="L17" s="68">
         <f t="shared" si="3"/>
-        <v>107124.55176499998</v>
+        <v>38500</v>
       </c>
       <c r="M17" s="25">
         <f t="shared" si="4"/>
-        <v>77000</v>
+        <v>106699.66037499999</v>
       </c>
       <c r="N17" s="25">
         <f t="shared" si="5"/>
-        <v>184124.55176499998</v>
-      </c>
-      <c r="P17" s="184"/>
-    </row>
-    <row r="18" spans="1:17" ht="15" customHeight="1">
-      <c r="A18" s="166">
+        <v>50455.319915</v>
+      </c>
+      <c r="O17" s="241">
+        <f t="shared" si="6"/>
+        <v>195654.98028999998</v>
+      </c>
+      <c r="Q17" s="183"/>
+    </row>
+    <row r="18" spans="1:18" ht="15" customHeight="1">
+      <c r="A18" s="165">
         <v>10</v>
       </c>
       <c r="B18" s="42" t="s">
@@ -4352,24 +4270,24 @@
       <c r="C18" s="94" t="s">
         <v>27</v>
       </c>
-      <c r="D18" s="168"/>
-      <c r="E18" s="169">
+      <c r="D18" s="167"/>
+      <c r="E18" s="168">
         <v>3.5900000000000001E-2</v>
       </c>
       <c r="F18" s="98">
-        <v>326928.01097983681</v>
-      </c>
-      <c r="G18" s="180">
-        <f>RESUMEN!H46+RESUMEN!H40+RESUMEN!H54</f>
+        <v>318869.51383709081</v>
+      </c>
+      <c r="G18" s="179">
+        <f>RESUMEN!H47+RESUMEN!H37+RESUMEN!H41</f>
         <v>185000</v>
       </c>
       <c r="H18" s="68">
         <f>IF(F18&gt;G18,F18-G18,0)</f>
-        <v>141928.01097983681</v>
+        <v>133869.51383709081</v>
       </c>
       <c r="I18" s="68">
-        <f t="shared" si="6"/>
-        <v>5251.3364062539622</v>
+        <f t="shared" si="7"/>
+        <v>4953.1720119723605</v>
       </c>
       <c r="J18" s="68">
         <f t="shared" si="1"/>
@@ -4379,71 +4297,79 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L18" s="170">
+      <c r="L18" s="68">
         <f t="shared" si="3"/>
-        <v>99890.166450999997</v>
-      </c>
-      <c r="M18" s="170">
+        <v>35900</v>
+      </c>
+      <c r="M18" s="169">
         <f t="shared" si="4"/>
-        <v>71800</v>
-      </c>
-      <c r="N18" s="170">
+        <v>99493.969024999999</v>
+      </c>
+      <c r="N18" s="169">
         <f t="shared" si="5"/>
-        <v>318869.51383709081</v>
-      </c>
-      <c r="P18" s="184"/>
-    </row>
-    <row r="19" spans="1:17" ht="15" customHeight="1">
-      <c r="A19" s="145">
+        <v>47047.947661000006</v>
+      </c>
+      <c r="O18" s="241">
+        <f t="shared" si="6"/>
+        <v>321264.60253506317</v>
+      </c>
+      <c r="Q18" s="183"/>
+    </row>
+    <row r="19" spans="1:18" ht="15" customHeight="1">
+      <c r="A19" s="144">
         <v>11</v>
       </c>
-      <c r="B19" s="152" t="s">
+      <c r="B19" s="151" t="s">
         <v>50</v>
       </c>
-      <c r="C19" s="153" t="s">
+      <c r="C19" s="152" t="s">
         <v>28</v>
       </c>
-      <c r="D19" s="155" t="s">
-        <v>110</v>
-      </c>
-      <c r="E19" s="156">
+      <c r="D19" s="154" t="s">
+        <v>109</v>
+      </c>
+      <c r="E19" s="155">
         <v>4.1399999999999999E-2</v>
       </c>
-      <c r="F19" s="149">
-        <v>2277755.8971485859</v>
-      </c>
-      <c r="G19" s="181"/>
-      <c r="H19" s="150">
+      <c r="F19" s="148">
+        <v>2560026.5391890835</v>
+      </c>
+      <c r="G19" s="180"/>
+      <c r="H19" s="149">
         <f t="shared" si="0"/>
-        <v>2277755.8971485859</v>
-      </c>
-      <c r="I19" s="150">
+        <v>2560026.5391890835</v>
+      </c>
+      <c r="I19" s="149">
+        <f t="shared" si="7"/>
+        <v>94720.981949996101</v>
+      </c>
+      <c r="J19" s="149">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K19" s="149">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L19" s="149">
+        <f t="shared" si="3"/>
+        <v>41400</v>
+      </c>
+      <c r="M19" s="150">
+        <f t="shared" si="4"/>
+        <v>114736.77765</v>
+      </c>
+      <c r="N19" s="150">
+        <f t="shared" si="5"/>
+        <v>54255.850506000002</v>
+      </c>
+      <c r="O19" s="242">
         <f t="shared" si="6"/>
-        <v>84276.968194497691</v>
-      </c>
-      <c r="J19" s="150">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K19" s="150">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="L19" s="151">
-        <f t="shared" si="3"/>
-        <v>115193.67384599999</v>
-      </c>
-      <c r="M19" s="151">
-        <f t="shared" si="4"/>
-        <v>82800</v>
-      </c>
-      <c r="N19" s="151">
-        <f t="shared" si="5"/>
-        <v>2560026.5391890835</v>
-      </c>
-      <c r="P19" s="184"/>
-    </row>
-    <row r="20" spans="1:17" ht="15" customHeight="1">
+        <v>2865140.14929508</v>
+      </c>
+      <c r="Q19" s="183"/>
+    </row>
+    <row r="20" spans="1:18" ht="15" customHeight="1">
       <c r="A20" s="51">
         <v>12</v>
       </c>
@@ -4451,27 +4377,27 @@
         <v>51</v>
       </c>
       <c r="C20" s="100" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D20" s="96" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E20" s="46">
         <v>5.3499999999999999E-2</v>
       </c>
       <c r="F20" s="17">
-        <v>233037.96857999999</v>
-      </c>
-      <c r="G20" s="180">
+        <v>255861.39011499999</v>
+      </c>
+      <c r="G20" s="179">
         <f>F20</f>
-        <v>233037.96857999999</v>
+        <v>255861.39011499999</v>
       </c>
       <c r="H20" s="24">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I20" s="24">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="J20" s="24">
@@ -4482,73 +4408,81 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L20" s="25">
+      <c r="L20" s="68">
         <f t="shared" si="3"/>
-        <v>148861.39011499999</v>
+        <v>53500</v>
       </c>
       <c r="M20" s="25">
         <f t="shared" si="4"/>
-        <v>107000</v>
+        <v>148270.95662499999</v>
       </c>
       <c r="N20" s="25">
         <f t="shared" si="5"/>
-        <v>255861.39011499999</v>
-      </c>
-      <c r="P20" s="184"/>
-    </row>
-    <row r="21" spans="1:17" ht="15" customHeight="1">
-      <c r="A21" s="145">
+        <v>70113.236764999994</v>
+      </c>
+      <c r="O20" s="241">
+        <f t="shared" si="6"/>
+        <v>271884.19338999997</v>
+      </c>
+      <c r="Q20" s="183"/>
+    </row>
+    <row r="21" spans="1:18" ht="15" customHeight="1">
+      <c r="A21" s="144">
         <v>13</v>
       </c>
-      <c r="B21" s="152" t="s">
+      <c r="B21" s="151" t="s">
         <v>52</v>
       </c>
-      <c r="C21" s="153" t="s">
+      <c r="C21" s="152" t="s">
         <v>30</v>
       </c>
-      <c r="D21" s="153" t="s">
-        <v>136</v>
-      </c>
-      <c r="E21" s="154">
+      <c r="D21" s="152" t="s">
+        <v>133</v>
+      </c>
+      <c r="E21" s="153">
         <v>3.85E-2</v>
       </c>
-      <c r="F21" s="149">
-        <v>1033990.2536342014</v>
-      </c>
-      <c r="G21" s="182">
-        <v>90700.72</v>
-      </c>
-      <c r="H21" s="150">
+      <c r="F21" s="148">
+        <v>1162315.7981436667</v>
+      </c>
+      <c r="G21" s="181">
+        <v>107124.55</v>
+      </c>
+      <c r="H21" s="149">
         <f t="shared" si="0"/>
-        <v>943289.53363420139</v>
-      </c>
-      <c r="I21" s="150">
+        <v>1055191.2481436667</v>
+      </c>
+      <c r="I21" s="149">
+        <f t="shared" si="7"/>
+        <v>39042.076181315671</v>
+      </c>
+      <c r="J21" s="149">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K21" s="149">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L21" s="149">
+        <f t="shared" si="3"/>
+        <v>38500</v>
+      </c>
+      <c r="M21" s="150">
+        <f t="shared" si="4"/>
+        <v>106699.66037499999</v>
+      </c>
+      <c r="N21" s="150">
+        <f t="shared" si="5"/>
+        <v>50455.319915</v>
+      </c>
+      <c r="O21" s="242">
         <f t="shared" si="6"/>
-        <v>34901.712744465454</v>
-      </c>
-      <c r="J21" s="150">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K21" s="150">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="L21" s="151">
-        <f t="shared" si="3"/>
-        <v>107124.55176499998</v>
-      </c>
-      <c r="M21" s="151">
-        <f t="shared" si="4"/>
-        <v>77000</v>
-      </c>
-      <c r="N21" s="151">
-        <f t="shared" si="5"/>
-        <v>1162315.7981436667</v>
-      </c>
-      <c r="P21" s="184"/>
-    </row>
-    <row r="22" spans="1:17" ht="15" customHeight="1">
+        <v>1289888.3046149821</v>
+      </c>
+      <c r="Q21" s="183"/>
+    </row>
+    <row r="22" spans="1:18" ht="15" customHeight="1">
       <c r="A22" s="51">
         <v>14</v>
       </c>
@@ -4559,24 +4493,24 @@
         <v>31</v>
       </c>
       <c r="D22" s="93" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E22" s="47">
         <v>3.5900000000000001E-2</v>
       </c>
       <c r="F22" s="17">
-        <v>156375.01069199998</v>
-      </c>
-      <c r="G22" s="180">
+        <v>171690.166451</v>
+      </c>
+      <c r="G22" s="179">
         <f>F22</f>
-        <v>156375.01069199998</v>
+        <v>171690.166451</v>
       </c>
       <c r="H22" s="24">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I22" s="24">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="J22" s="24">
@@ -4587,21 +4521,25 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L22" s="25">
+      <c r="L22" s="68">
         <f t="shared" si="3"/>
-        <v>99890.166450999997</v>
+        <v>35900</v>
       </c>
       <c r="M22" s="25">
         <f t="shared" si="4"/>
-        <v>71800</v>
+        <v>99493.969024999999</v>
       </c>
       <c r="N22" s="25">
         <f t="shared" si="5"/>
-        <v>171690.166451</v>
-      </c>
-      <c r="P22" s="184"/>
-    </row>
-    <row r="23" spans="1:17" ht="15" customHeight="1">
+        <v>47047.947661000006</v>
+      </c>
+      <c r="O22" s="241">
+        <f t="shared" si="6"/>
+        <v>182441.91668600001</v>
+      </c>
+      <c r="Q22" s="183"/>
+    </row>
+    <row r="23" spans="1:18" ht="15" customHeight="1">
       <c r="A23" s="51">
         <v>15</v>
       </c>
@@ -4612,24 +4550,24 @@
         <v>32</v>
       </c>
       <c r="D23" s="94" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E23" s="48">
         <v>4.1399999999999999E-2</v>
       </c>
       <c r="F23" s="17">
-        <v>273206.61445009825</v>
-      </c>
-      <c r="G23" s="180">
+        <v>197993.67384599999</v>
+      </c>
+      <c r="G23" s="179">
         <f>F23</f>
-        <v>273206.61445009825</v>
+        <v>197993.67384599999</v>
       </c>
       <c r="H23" s="24">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I23" s="24">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="J23" s="24">
@@ -4640,21 +4578,25 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L23" s="25">
+      <c r="L23" s="68">
         <f t="shared" si="3"/>
-        <v>115193.67384599999</v>
+        <v>41400</v>
       </c>
       <c r="M23" s="25">
         <f t="shared" si="4"/>
-        <v>82800</v>
+        <v>114736.77765</v>
       </c>
       <c r="N23" s="25">
         <f t="shared" si="5"/>
-        <v>197993.67384599999</v>
-      </c>
-      <c r="P23" s="184"/>
-    </row>
-    <row r="24" spans="1:17" ht="15" customHeight="1">
+        <v>54255.850506000002</v>
+      </c>
+      <c r="O23" s="241">
+        <f t="shared" si="6"/>
+        <v>210392.62815599999</v>
+      </c>
+      <c r="Q23" s="183"/>
+    </row>
+    <row r="24" spans="1:18" ht="15" customHeight="1">
       <c r="A24" s="51">
         <v>16</v>
       </c>
@@ -4669,18 +4611,18 @@
         <v>5.3499999999999999E-2</v>
       </c>
       <c r="F24" s="17">
-        <v>233037.96857999999</v>
-      </c>
-      <c r="G24" s="180">
+        <v>255861.39011499999</v>
+      </c>
+      <c r="G24" s="179">
         <f>F24</f>
-        <v>233037.96857999999</v>
+        <v>255861.39011499999</v>
       </c>
       <c r="H24" s="24">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I24" s="24">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="J24" s="24">
@@ -4691,21 +4633,25 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L24" s="25">
+      <c r="L24" s="68">
         <f t="shared" si="3"/>
-        <v>148861.39011499999</v>
+        <v>53500</v>
       </c>
       <c r="M24" s="25">
         <f t="shared" si="4"/>
-        <v>107000</v>
+        <v>148270.95662499999</v>
       </c>
       <c r="N24" s="25">
         <f t="shared" si="5"/>
-        <v>255861.39011499999</v>
-      </c>
-      <c r="P24" s="184"/>
-    </row>
-    <row r="25" spans="1:17" s="1" customFormat="1" ht="15.75" customHeight="1">
+        <v>70113.236764999994</v>
+      </c>
+      <c r="O24" s="241">
+        <f t="shared" si="6"/>
+        <v>271884.19338999997</v>
+      </c>
+      <c r="Q24" s="183"/>
+    </row>
+    <row r="25" spans="1:18" s="1" customFormat="1" ht="15.75" customHeight="1">
       <c r="A25" s="51">
         <v>17</v>
       </c>
@@ -4713,27 +4659,27 @@
         <v>56</v>
       </c>
       <c r="C25" s="95" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D25" s="95" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E25" s="49">
         <v>3.85E-2</v>
       </c>
       <c r="F25" s="17">
-        <v>167700.22038000001</v>
-      </c>
-      <c r="G25" s="180">
+        <v>184124.55176499998</v>
+      </c>
+      <c r="G25" s="179">
         <f>F25</f>
-        <v>167700.22038000001</v>
+        <v>184124.55176499998</v>
       </c>
       <c r="H25" s="24">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I25" s="24">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="J25" s="24">
@@ -4744,21 +4690,25 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L25" s="25">
+      <c r="L25" s="68">
         <f t="shared" si="3"/>
-        <v>107124.55176499998</v>
+        <v>38500</v>
       </c>
       <c r="M25" s="25">
         <f t="shared" si="4"/>
-        <v>77000</v>
+        <v>106699.66037499999</v>
       </c>
       <c r="N25" s="25">
         <f t="shared" si="5"/>
-        <v>184124.55176499998</v>
-      </c>
-      <c r="P25" s="185"/>
-    </row>
-    <row r="26" spans="1:17" ht="15" customHeight="1">
+        <v>50455.319915</v>
+      </c>
+      <c r="O25" s="241">
+        <f t="shared" si="6"/>
+        <v>195654.98028999998</v>
+      </c>
+      <c r="Q25" s="184"/>
+    </row>
+    <row r="26" spans="1:18" ht="15" customHeight="1">
       <c r="A26" s="51">
         <v>18</v>
       </c>
@@ -4773,18 +4723,18 @@
         <v>3.5900000000000001E-2</v>
       </c>
       <c r="F26" s="17">
-        <v>156375.01069199998</v>
-      </c>
-      <c r="G26" s="180">
+        <v>171690.166451</v>
+      </c>
+      <c r="G26" s="179">
         <f>F26</f>
-        <v>156375.01069199998</v>
+        <v>171690.166451</v>
       </c>
       <c r="H26" s="24">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I26" s="24">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="J26" s="24">
@@ -4795,76 +4745,84 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L26" s="25">
+      <c r="L26" s="68">
         <f t="shared" si="3"/>
-        <v>99890.166450999997</v>
+        <v>35900</v>
       </c>
       <c r="M26" s="25">
         <f t="shared" si="4"/>
-        <v>71800</v>
+        <v>99493.969024999999</v>
       </c>
       <c r="N26" s="25">
         <f t="shared" si="5"/>
-        <v>171690.166451</v>
-      </c>
-      <c r="P26" s="184"/>
-    </row>
-    <row r="27" spans="1:17" ht="15" customHeight="1">
-      <c r="A27" s="145">
+        <v>47047.947661000006</v>
+      </c>
+      <c r="O26" s="241">
+        <f t="shared" si="6"/>
+        <v>182441.91668600001</v>
+      </c>
+      <c r="Q26" s="183"/>
+    </row>
+    <row r="27" spans="1:18" ht="15" customHeight="1">
+      <c r="A27" s="144">
         <v>19</v>
       </c>
-      <c r="B27" s="146" t="s">
+      <c r="B27" s="145" t="s">
         <v>58</v>
       </c>
-      <c r="C27" s="147" t="s">
+      <c r="C27" s="146" t="s">
         <v>35</v>
       </c>
-      <c r="D27" s="147" t="s">
-        <v>126</v>
-      </c>
-      <c r="E27" s="148">
+      <c r="D27" s="146" t="s">
+        <v>124</v>
+      </c>
+      <c r="E27" s="147">
         <v>4.1399999999999999E-2</v>
       </c>
-      <c r="F27" s="149">
-        <v>2927531.1491925181</v>
-      </c>
-      <c r="G27" s="181">
-        <v>180332</v>
-      </c>
-      <c r="H27" s="172">
+      <c r="F27" s="148">
+        <v>3046839.1915586414</v>
+      </c>
+      <c r="G27" s="180">
+        <v>197993.67</v>
+      </c>
+      <c r="H27" s="171">
         <f t="shared" si="0"/>
-        <v>2747199.1491925181</v>
-      </c>
-      <c r="I27" s="150">
+        <v>2848845.5215586415</v>
+      </c>
+      <c r="I27" s="149">
+        <f t="shared" si="7"/>
+        <v>105407.28429766974</v>
+      </c>
+      <c r="J27" s="149">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K27" s="149">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L27" s="149">
+        <f t="shared" si="3"/>
+        <v>41400</v>
+      </c>
+      <c r="M27" s="150">
+        <f t="shared" si="4"/>
+        <v>114736.77765</v>
+      </c>
+      <c r="N27" s="150">
+        <f t="shared" si="5"/>
+        <v>54255.850506000002</v>
+      </c>
+      <c r="O27" s="242">
         <f t="shared" si="6"/>
-        <v>101646.36852012319</v>
-      </c>
-      <c r="J27" s="150">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K27" s="150">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="L27" s="151">
-        <f t="shared" si="3"/>
-        <v>115193.67384599999</v>
-      </c>
-      <c r="M27" s="151">
-        <f t="shared" si="4"/>
-        <v>82800</v>
-      </c>
-      <c r="N27" s="151">
-        <f t="shared" si="5"/>
-        <v>3046839.1915586414</v>
-      </c>
-      <c r="O27" s="186">
-        <f>L27+M27</f>
-        <v>197993.67384599999</v>
-      </c>
-    </row>
-    <row r="28" spans="1:17" ht="17.25" customHeight="1">
+        <v>3164645.4340123115</v>
+      </c>
+      <c r="P27" s="185">
+        <f>M27+N27</f>
+        <v>168992.62815599999</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" ht="17.25" customHeight="1">
       <c r="A28" s="51">
         <v>20</v>
       </c>
@@ -4879,37 +4837,41 @@
         <v>5.3499999999999999E-2</v>
       </c>
       <c r="F28" s="17">
-        <v>1353936.2987744827</v>
-      </c>
-      <c r="G28" s="180"/>
+        <v>1659893.3319441385</v>
+      </c>
+      <c r="G28" s="179"/>
       <c r="H28" s="68">
         <f t="shared" si="0"/>
-        <v>1353936.2987744827</v>
+        <v>1659893.3319441385</v>
       </c>
       <c r="I28" s="24">
-        <f t="shared" si="6"/>
-        <v>50095.643054655869</v>
+        <f t="shared" si="7"/>
+        <v>61416.053281933135</v>
       </c>
       <c r="J28" s="24">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="K28" s="24"/>
-      <c r="L28" s="25">
+      <c r="L28" s="68">
         <f t="shared" si="3"/>
-        <v>148861.39011499999</v>
+        <v>53500</v>
       </c>
       <c r="M28" s="25">
         <f t="shared" si="4"/>
-        <v>107000</v>
+        <v>148270.95662499999</v>
       </c>
       <c r="N28" s="25">
         <f t="shared" si="5"/>
-        <v>1659893.3319441385</v>
-      </c>
-      <c r="O28" s="7"/>
-    </row>
-    <row r="29" spans="1:17" ht="15" customHeight="1">
+        <v>70113.236764999994</v>
+      </c>
+      <c r="O28" s="241">
+        <f t="shared" si="6"/>
+        <v>1993193.5786160715</v>
+      </c>
+      <c r="P28" s="7"/>
+    </row>
+    <row r="29" spans="1:18" ht="15" customHeight="1">
       <c r="A29" s="51">
         <v>21</v>
       </c>
@@ -4917,25 +4879,25 @@
         <v>60</v>
       </c>
       <c r="C29" s="95" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D29" s="95"/>
       <c r="E29" s="49">
         <v>3.85E-2</v>
       </c>
       <c r="F29" s="17">
-        <v>167700.22038000001</v>
-      </c>
-      <c r="G29" s="180">
+        <v>184124.55176499998</v>
+      </c>
+      <c r="G29" s="179">
         <f>F29</f>
-        <v>167700.22038000001</v>
+        <v>184124.55176499998</v>
       </c>
       <c r="H29" s="24">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I29" s="24">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="J29" s="24">
@@ -4946,28 +4908,32 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L29" s="25">
+      <c r="L29" s="68">
         <f t="shared" si="3"/>
-        <v>107124.55176499998</v>
+        <v>38500</v>
       </c>
       <c r="M29" s="25">
         <f t="shared" si="4"/>
-        <v>77000</v>
+        <v>106699.66037499999</v>
       </c>
       <c r="N29" s="25">
         <f t="shared" si="5"/>
-        <v>184124.55176499998</v>
-      </c>
-      <c r="O29" s="7"/>
-      <c r="P29" s="7">
-        <f>SUM(P15:P28)</f>
-        <v>923746</v>
-      </c>
-      <c r="Q29" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="30" spans="1:17" ht="15" customHeight="1">
+        <v>50455.319915</v>
+      </c>
+      <c r="O29" s="241">
+        <f t="shared" si="6"/>
+        <v>195654.98028999998</v>
+      </c>
+      <c r="P29" s="7"/>
+      <c r="Q29" s="7">
+        <f>SUM(Q15:Q28)</f>
+        <v>0</v>
+      </c>
+      <c r="R29" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" ht="15" customHeight="1">
       <c r="A30" s="51">
         <v>22</v>
       </c>
@@ -4975,27 +4941,27 @@
         <v>61</v>
       </c>
       <c r="C30" s="95" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D30" s="95" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E30" s="49">
         <v>3.5900000000000001E-2</v>
       </c>
       <c r="F30" s="17">
-        <v>156375.01069199998</v>
-      </c>
-      <c r="G30" s="180">
+        <v>171690.166451</v>
+      </c>
+      <c r="G30" s="179">
         <f>F30</f>
-        <v>156375.01069199998</v>
+        <v>171690.166451</v>
       </c>
       <c r="H30" s="24">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I30" s="24">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="J30" s="24">
@@ -5006,20 +4972,24 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L30" s="25">
+      <c r="L30" s="68">
         <f t="shared" si="3"/>
-        <v>99890.166450999997</v>
+        <v>35900</v>
       </c>
       <c r="M30" s="25">
         <f t="shared" si="4"/>
-        <v>71800</v>
+        <v>99493.969024999999</v>
       </c>
       <c r="N30" s="25">
         <f t="shared" si="5"/>
-        <v>171690.166451</v>
-      </c>
-    </row>
-    <row r="31" spans="1:17" ht="15" customHeight="1">
+        <v>47047.947661000006</v>
+      </c>
+      <c r="O30" s="241">
+        <f t="shared" si="6"/>
+        <v>182441.91668600001</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" ht="15" customHeight="1">
       <c r="A31" s="51">
         <v>23</v>
       </c>
@@ -5034,18 +5004,18 @@
         <v>4.1399999999999999E-2</v>
       </c>
       <c r="F31" s="17">
-        <v>180332.18503200001</v>
-      </c>
-      <c r="G31" s="180">
+        <v>197993.67384599999</v>
+      </c>
+      <c r="G31" s="179">
         <f>F31</f>
-        <v>180332.18503200001</v>
+        <v>197993.67384599999</v>
       </c>
       <c r="H31" s="24">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I31" s="24">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="J31" s="24">
@@ -5056,20 +5026,24 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L31" s="25">
+      <c r="L31" s="68">
         <f t="shared" si="3"/>
-        <v>115193.67384599999</v>
+        <v>41400</v>
       </c>
       <c r="M31" s="25">
         <f t="shared" si="4"/>
-        <v>82800</v>
+        <v>114736.77765</v>
       </c>
       <c r="N31" s="25">
         <f t="shared" si="5"/>
-        <v>197993.67384599999</v>
-      </c>
-    </row>
-    <row r="32" spans="1:17" ht="15.6">
+        <v>54255.850506000002</v>
+      </c>
+      <c r="O31" s="241">
+        <f t="shared" si="6"/>
+        <v>210392.62815599999</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" ht="15.6">
       <c r="A32" s="37"/>
       <c r="B32" s="52">
         <f>SUM(B9:B31)</f>
@@ -5083,163 +5057,174 @@
       </c>
       <c r="F32" s="99">
         <f>SUM(F9:F31)</f>
-        <v>14455762.054366976</v>
+        <v>15883307.414084934</v>
       </c>
       <c r="G32" s="99">
         <f>SUM(G9:G31)</f>
-        <v>3671141.4911220977</v>
-      </c>
-      <c r="H32" s="124">
+        <v>3926249.2638619998</v>
+      </c>
+      <c r="H32" s="123">
         <f>SUM(H9:H31)</f>
-        <v>10784620.563244874</v>
+        <v>11957058.150222933</v>
       </c>
       <c r="I32" s="54">
         <f>SUM(I9:I31)</f>
-        <v>399030.96084006038</v>
+        <v>442411.15155824862</v>
       </c>
       <c r="J32" s="99">
-        <f t="shared" ref="J32" si="7">SUM(J9:J31)</f>
+        <f t="shared" ref="J32" si="8">SUM(J9:J31)</f>
         <v>0</v>
       </c>
       <c r="K32" s="90">
         <f>SUM(K9:K31)</f>
         <v>0</v>
       </c>
-      <c r="L32" s="54">
-        <f>SUM(L9:L31)</f>
-        <v>2782455.8899999992</v>
-      </c>
-      <c r="M32" s="90">
+      <c r="L32" s="90"/>
+      <c r="M32" s="54">
         <f>SUM(M9:M31)</f>
-        <v>1917200</v>
-      </c>
-      <c r="N32" s="54">
+        <v>2771419.7500000005</v>
+      </c>
+      <c r="N32" s="90">
         <f>SUM(N9:N31)</f>
-        <v>15883307.414084934</v>
-      </c>
-    </row>
-    <row r="33" spans="1:14" ht="14.25" customHeight="1"/>
-    <row r="34" spans="1:14" hidden="1">
-      <c r="B34" s="229"/>
-      <c r="C34" s="229"/>
-      <c r="D34" s="229"/>
-      <c r="E34" s="229"/>
-      <c r="F34" s="229"/>
-      <c r="G34" s="229"/>
-      <c r="H34" s="229"/>
-      <c r="I34" s="229"/>
-      <c r="J34" s="229"/>
-      <c r="K34" s="229"/>
-      <c r="L34" s="229"/>
-      <c r="M34" s="229"/>
-      <c r="N34" s="229"/>
-    </row>
-    <row r="35" spans="1:14" hidden="1">
-      <c r="B35" s="229"/>
-      <c r="C35" s="229"/>
-      <c r="D35" s="229"/>
-      <c r="E35" s="229"/>
-      <c r="F35" s="229"/>
-      <c r="G35" s="229"/>
-      <c r="H35" s="229"/>
-      <c r="I35" s="229"/>
-      <c r="J35" s="229"/>
-      <c r="K35" s="229"/>
-      <c r="L35" s="229"/>
-      <c r="M35" s="229"/>
-      <c r="N35" s="229"/>
-    </row>
-    <row r="36" spans="1:14" hidden="1">
-      <c r="B36" s="229"/>
-      <c r="C36" s="229"/>
-      <c r="D36" s="229"/>
-      <c r="E36" s="229"/>
-      <c r="F36" s="229"/>
-      <c r="G36" s="229"/>
-      <c r="H36" s="229"/>
-      <c r="I36" s="229"/>
-      <c r="J36" s="229"/>
-      <c r="K36" s="229"/>
-      <c r="L36" s="229"/>
-      <c r="M36" s="229"/>
-      <c r="N36" s="229"/>
-    </row>
-    <row r="37" spans="1:14" hidden="1">
-      <c r="B37" s="229"/>
-      <c r="C37" s="229"/>
-      <c r="D37" s="229"/>
-      <c r="E37" s="229"/>
-      <c r="F37" s="229"/>
-      <c r="G37" s="229"/>
-      <c r="H37" s="229"/>
-      <c r="I37" s="229"/>
-      <c r="J37" s="229"/>
-      <c r="K37" s="229"/>
-      <c r="L37" s="229"/>
-      <c r="M37" s="229"/>
-      <c r="N37" s="229"/>
-    </row>
-    <row r="38" spans="1:14" hidden="1">
-      <c r="A38" s="231"/>
-      <c r="B38" s="231"/>
-      <c r="C38" s="231"/>
-      <c r="D38" s="231"/>
-      <c r="E38" s="231"/>
-      <c r="F38" s="231"/>
-      <c r="G38" s="231"/>
-      <c r="H38" s="231"/>
-      <c r="I38" s="231"/>
-      <c r="J38" s="231"/>
-      <c r="K38" s="231"/>
-      <c r="L38" s="231"/>
-      <c r="M38" s="231"/>
-      <c r="N38" s="231"/>
-    </row>
-    <row r="39" spans="1:14" hidden="1">
-      <c r="A39" s="231"/>
-      <c r="B39" s="231"/>
-      <c r="C39" s="231"/>
-      <c r="D39" s="231"/>
-      <c r="E39" s="231"/>
-      <c r="F39" s="231"/>
-      <c r="G39" s="231"/>
-      <c r="H39" s="231"/>
-      <c r="I39" s="231"/>
-      <c r="J39" s="231"/>
-      <c r="K39" s="231"/>
-      <c r="L39" s="231"/>
-      <c r="M39" s="231"/>
-      <c r="N39" s="231"/>
-    </row>
-    <row r="40" spans="1:14" hidden="1">
-      <c r="A40" s="231"/>
-      <c r="B40" s="231"/>
-      <c r="C40" s="231"/>
-      <c r="D40" s="231"/>
-      <c r="E40" s="231"/>
-      <c r="F40" s="231"/>
-      <c r="G40" s="231"/>
-      <c r="H40" s="231"/>
-      <c r="I40" s="231"/>
-      <c r="J40" s="231"/>
-      <c r="K40" s="231"/>
-      <c r="L40" s="231"/>
-      <c r="M40" s="231"/>
-      <c r="N40" s="231"/>
-    </row>
-    <row r="41" spans="1:14">
-      <c r="N41" s="7"/>
+        <v>1256271.9394939998</v>
+      </c>
+      <c r="O32" s="54">
+        <f>SUM(O9:O31)</f>
+        <v>17427160.99127518</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" ht="14.25" customHeight="1"/>
+    <row r="34" spans="1:15" hidden="1">
+      <c r="B34" s="228"/>
+      <c r="C34" s="228"/>
+      <c r="D34" s="228"/>
+      <c r="E34" s="228"/>
+      <c r="F34" s="228"/>
+      <c r="G34" s="228"/>
+      <c r="H34" s="228"/>
+      <c r="I34" s="228"/>
+      <c r="J34" s="228"/>
+      <c r="K34" s="228"/>
+      <c r="L34" s="228"/>
+      <c r="M34" s="228"/>
+      <c r="N34" s="228"/>
+      <c r="O34" s="228"/>
+    </row>
+    <row r="35" spans="1:15" hidden="1">
+      <c r="B35" s="228"/>
+      <c r="C35" s="228"/>
+      <c r="D35" s="228"/>
+      <c r="E35" s="228"/>
+      <c r="F35" s="228"/>
+      <c r="G35" s="228"/>
+      <c r="H35" s="228"/>
+      <c r="I35" s="228"/>
+      <c r="J35" s="228"/>
+      <c r="K35" s="228"/>
+      <c r="L35" s="228"/>
+      <c r="M35" s="228"/>
+      <c r="N35" s="228"/>
+      <c r="O35" s="228"/>
+    </row>
+    <row r="36" spans="1:15" hidden="1">
+      <c r="B36" s="228"/>
+      <c r="C36" s="228"/>
+      <c r="D36" s="228"/>
+      <c r="E36" s="228"/>
+      <c r="F36" s="228"/>
+      <c r="G36" s="228"/>
+      <c r="H36" s="228"/>
+      <c r="I36" s="228"/>
+      <c r="J36" s="228"/>
+      <c r="K36" s="228"/>
+      <c r="L36" s="228"/>
+      <c r="M36" s="228"/>
+      <c r="N36" s="228"/>
+      <c r="O36" s="228"/>
+    </row>
+    <row r="37" spans="1:15" hidden="1">
+      <c r="B37" s="228"/>
+      <c r="C37" s="228"/>
+      <c r="D37" s="228"/>
+      <c r="E37" s="228"/>
+      <c r="F37" s="228"/>
+      <c r="G37" s="228"/>
+      <c r="H37" s="228"/>
+      <c r="I37" s="228"/>
+      <c r="J37" s="228"/>
+      <c r="K37" s="228"/>
+      <c r="L37" s="228"/>
+      <c r="M37" s="228"/>
+      <c r="N37" s="228"/>
+      <c r="O37" s="228"/>
+    </row>
+    <row r="38" spans="1:15" hidden="1">
+      <c r="A38" s="230"/>
+      <c r="B38" s="230"/>
+      <c r="C38" s="230"/>
+      <c r="D38" s="230"/>
+      <c r="E38" s="230"/>
+      <c r="F38" s="230"/>
+      <c r="G38" s="230"/>
+      <c r="H38" s="230"/>
+      <c r="I38" s="230"/>
+      <c r="J38" s="230"/>
+      <c r="K38" s="230"/>
+      <c r="L38" s="230"/>
+      <c r="M38" s="230"/>
+      <c r="N38" s="230"/>
+      <c r="O38" s="230"/>
+    </row>
+    <row r="39" spans="1:15" hidden="1">
+      <c r="A39" s="230"/>
+      <c r="B39" s="230"/>
+      <c r="C39" s="230"/>
+      <c r="D39" s="230"/>
+      <c r="E39" s="230"/>
+      <c r="F39" s="230"/>
+      <c r="G39" s="230"/>
+      <c r="H39" s="230"/>
+      <c r="I39" s="230"/>
+      <c r="J39" s="230"/>
+      <c r="K39" s="230"/>
+      <c r="L39" s="230"/>
+      <c r="M39" s="230"/>
+      <c r="N39" s="230"/>
+      <c r="O39" s="230"/>
+    </row>
+    <row r="40" spans="1:15" hidden="1">
+      <c r="A40" s="230"/>
+      <c r="B40" s="230"/>
+      <c r="C40" s="230"/>
+      <c r="D40" s="230"/>
+      <c r="E40" s="230"/>
+      <c r="F40" s="230"/>
+      <c r="G40" s="230"/>
+      <c r="H40" s="230"/>
+      <c r="I40" s="230"/>
+      <c r="J40" s="230"/>
+      <c r="K40" s="230"/>
+      <c r="L40" s="230"/>
+      <c r="M40" s="230"/>
+      <c r="N40" s="230"/>
+      <c r="O40" s="230"/>
+    </row>
+    <row r="41" spans="1:15">
+      <c r="O41" s="7"/>
     </row>
   </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="B34:N37"/>
+  <mergeCells count="8">
+    <mergeCell ref="B34:O37"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B7:C7"/>
-    <mergeCell ref="A38:N40"/>
+    <mergeCell ref="A38:O40"/>
     <mergeCell ref="B6:C6"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="E5:F5"/>
   </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="65" orientation="landscape" r:id="rId1"/>
+  <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="3" orientation="landscape" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>
@@ -5257,15 +5242,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="34.5" customHeight="1" thickBot="1">
-      <c r="A1" s="234" t="s">
-        <v>91</v>
-      </c>
-      <c r="B1" s="235"/>
-      <c r="C1" s="235"/>
-      <c r="D1" s="235"/>
-      <c r="E1" s="235"/>
-      <c r="F1" s="235"/>
-      <c r="G1" s="236"/>
+      <c r="A1" s="233" t="s">
+        <v>90</v>
+      </c>
+      <c r="B1" s="234"/>
+      <c r="C1" s="234"/>
+      <c r="D1" s="234"/>
+      <c r="E1" s="234"/>
+      <c r="F1" s="234"/>
+      <c r="G1" s="235"/>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="30"/>
@@ -5274,7 +5259,7 @@
     <row r="3" spans="1:7">
       <c r="A3" s="57"/>
       <c r="B3" s="59" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G3" s="31"/>
     </row>
@@ -5324,7 +5309,7 @@
         <v>15</v>
       </c>
       <c r="F8" s="74" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G8" s="29" t="s">
         <v>8</v>
@@ -5349,7 +5334,7 @@
       </c>
       <c r="F9" s="70"/>
       <c r="G9" s="70" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -5371,7 +5356,7 @@
       </c>
       <c r="F10" s="70"/>
       <c r="G10" s="70" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -5393,7 +5378,7 @@
       </c>
       <c r="F11" s="70"/>
       <c r="G11" s="70" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -5415,7 +5400,7 @@
       </c>
       <c r="F12" s="70"/>
       <c r="G12" s="70" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -5437,7 +5422,7 @@
       </c>
       <c r="F13" s="70"/>
       <c r="G13" s="70" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -5485,7 +5470,7 @@
       </c>
       <c r="F15" s="70"/>
       <c r="G15" s="70" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -5496,7 +5481,7 @@
         <v>47</v>
       </c>
       <c r="C16" s="34" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D16" s="45">
         <v>5.3499999999999999E-2</v>
@@ -5507,7 +5492,7 @@
       </c>
       <c r="F16" s="70"/>
       <c r="G16" s="70" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -5529,7 +5514,7 @@
       </c>
       <c r="F17" s="70"/>
       <c r="G17" s="70" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -5551,7 +5536,7 @@
       </c>
       <c r="F18" s="70"/>
       <c r="G18" s="70" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -5599,7 +5584,7 @@
       </c>
       <c r="F20" s="70"/>
       <c r="G20" s="70" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -5621,7 +5606,7 @@
       </c>
       <c r="F21" s="70"/>
       <c r="G21" s="70" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -5643,7 +5628,7 @@
       </c>
       <c r="F22" s="70"/>
       <c r="G22" s="70" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -5665,7 +5650,7 @@
       </c>
       <c r="F23" s="70"/>
       <c r="G23" s="70" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="15.6">
@@ -5687,7 +5672,7 @@
       </c>
       <c r="F24" s="70"/>
       <c r="G24" s="70" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="15.6">
@@ -5698,7 +5683,7 @@
         <v>56</v>
       </c>
       <c r="C25" s="65" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D25" s="49">
         <v>3.85E-2</v>
@@ -5709,7 +5694,7 @@
       </c>
       <c r="F25" s="70"/>
       <c r="G25" s="70" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="15.6">
@@ -5731,7 +5716,7 @@
       </c>
       <c r="F26" s="70"/>
       <c r="G26" s="70" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="15.6">
@@ -5779,7 +5764,7 @@
       </c>
       <c r="F28" s="70"/>
       <c r="G28" s="70" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="15.6">
@@ -5801,7 +5786,7 @@
       </c>
       <c r="F29" s="70"/>
       <c r="G29" s="70" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="30" spans="1:7" ht="15.6">
@@ -5823,7 +5808,7 @@
       </c>
       <c r="F30" s="70"/>
       <c r="G30" s="70" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="15.6">
@@ -5845,7 +5830,7 @@
       </c>
       <c r="F31" s="70"/>
       <c r="G31" s="70" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="15.6">
@@ -5868,7 +5853,7 @@
     </row>
     <row r="34" spans="3:5" ht="13.5" customHeight="1">
       <c r="C34" s="77" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D34" s="75"/>
       <c r="E34" s="76">
